--- a/output/yearly_surface_area_iteration_57_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_57_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497640131867</v>
+        <v>10.84497640384105</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907218269945</v>
+        <v>37.78907219148862</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.375068680751286</v>
+        <v>6.927211801165494</v>
       </c>
       <c r="C2" t="n">
-        <v>10.82376843932108</v>
+        <v>5.667629496616836</v>
       </c>
       <c r="D2" t="n">
-        <v>24.81956371106361</v>
+        <v>22.90908267859932</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.74647241259284</v>
+        <v>24.78422079371073</v>
       </c>
       <c r="C3" t="n">
-        <v>36.03995822290041</v>
+        <v>17.56346642897544</v>
       </c>
       <c r="D3" t="n">
-        <v>85.91274159863838</v>
+        <v>79.78172718561706</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.60722846950582</v>
+        <v>48.79187915336223</v>
       </c>
       <c r="C4" t="n">
-        <v>85.3698351181899</v>
+        <v>41.78514578815274</v>
       </c>
       <c r="D4" t="n">
-        <v>126.7338111412208</v>
+        <v>105.7518992060579</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.3076565509903</v>
+        <v>58.90486225480863</v>
       </c>
       <c r="C5" t="n">
-        <v>127.5044830890545</v>
+        <v>98.91108120286617</v>
       </c>
       <c r="D5" t="n">
-        <v>93.65873098514572</v>
+        <v>71.15216486528759</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.96360288614742</v>
+        <v>54.66174867705392</v>
       </c>
       <c r="C6" t="n">
-        <v>135.4468220164112</v>
+        <v>138.425444551096</v>
       </c>
       <c r="D6" t="n">
-        <v>56.79508643838223</v>
+        <v>46.65166915810419</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.99078872223005</v>
+        <v>38.80652325346792</v>
       </c>
       <c r="C7" t="n">
-        <v>101.6275771005171</v>
+        <v>119.7133333081518</v>
       </c>
       <c r="D7" t="n">
-        <v>41.08221443191203</v>
+        <v>38.86640986342697</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.01797455831271</v>
+        <v>20.11110172149591</v>
       </c>
       <c r="C8" t="n">
-        <v>59.248473951295</v>
+        <v>74.51955949085414</v>
       </c>
       <c r="D8" t="n">
-        <v>36.30012136452581</v>
+        <v>35.46563581591602</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.989061906533041</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
-        <v>35.94374694788421</v>
+        <v>41.15780900513902</v>
       </c>
       <c r="D9" t="n">
         <v>33.72499713628642</v>
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
         <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
         <v>32.26022956155019</v>
@@ -951,7 +951,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>22.73924032576462</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.659260130238023</v>
+        <v>7.656393479920259</v>
       </c>
       <c r="C21" t="n">
-        <v>92.86852907913602</v>
+        <v>92.83377094403313</v>
       </c>
       <c r="D21" t="n">
-        <v>7.659260130238023</v>
+        <v>7.656393479920259</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.190320185903639</v>
+        <v>8.931940613237481</v>
       </c>
       <c r="C2" t="n">
-        <v>9.277515805132358</v>
+        <v>9.141052874242051</v>
       </c>
       <c r="D2" t="n">
-        <v>36.50432488700915</v>
+        <v>27.42021337961341</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.18196748265093</v>
+        <v>23.81719930502762</v>
       </c>
       <c r="C3" t="n">
-        <v>38.76921684070655</v>
+        <v>19.70367642423349</v>
       </c>
       <c r="D3" t="n">
-        <v>85.16170460488956</v>
+        <v>79.14359117785662</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.66729500591412</v>
+        <v>47.86020058203201</v>
       </c>
       <c r="C4" t="n">
-        <v>87.42463306317846</v>
+        <v>42.72958707963818</v>
       </c>
       <c r="D4" t="n">
-        <v>136.4972920599553</v>
+        <v>119.1272299287165</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.02633692822798</v>
+        <v>64.91806694332035</v>
       </c>
       <c r="C5" t="n">
-        <v>139.8008730847458</v>
+        <v>87.52280783360315</v>
       </c>
       <c r="D5" t="n">
-        <v>113.8581900000239</v>
+        <v>88.60273030827464</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.42274201656544</v>
+        <v>65.73095404243671</v>
       </c>
       <c r="C6" t="n">
-        <v>164.6292725251477</v>
+        <v>147.5625704345211</v>
       </c>
       <c r="D6" t="n">
-        <v>69.39385472698156</v>
+        <v>56.75483478250812</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.85400699617026</v>
+        <v>51.08327829507428</v>
       </c>
       <c r="C7" t="n">
-        <v>144.6261630511189</v>
+        <v>155.6452992835851</v>
       </c>
       <c r="D7" t="n">
-        <v>47.01098881785852</v>
+        <v>42.51949307092936</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.61041039233004</v>
+        <v>29.70768553050848</v>
       </c>
       <c r="C8" t="n">
-        <v>92.54444734082557</v>
+        <v>113.3231375012093</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>37.80219535202343</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.762499171030278</v>
+        <v>13.86718632248619</v>
       </c>
       <c r="C9" t="n">
-        <v>53.0281204971872</v>
+        <v>63.89999457401638</v>
       </c>
       <c r="D9" t="n">
-        <v>35.27812200440487</v>
+        <v>34.83437204208531</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.978843518863076</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>35.58835427894688</v>
+        <v>39.00483628972578</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1223,7 +1223,7 @@
         <v>31.98534020436108</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.94134148411922</v>
+        <v>29.72437524148068</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1276,7 +1276,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -1293,7 +1293,7 @@
         <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.830404843371868</v>
+        <v>7.831115815995572</v>
       </c>
       <c r="C21" t="n">
-        <v>100.8164623584128</v>
+        <v>100.825616130943</v>
       </c>
       <c r="D21" t="n">
-        <v>8.809205448793351</v>
+        <v>8.810005292995019</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.170505305369456</v>
+        <v>9.310895227076751</v>
       </c>
       <c r="C2" t="n">
-        <v>5.790347959647687</v>
+        <v>7.498588965037137</v>
       </c>
       <c r="D2" t="n">
-        <v>46.79794956603696</v>
+        <v>23.89573912136737</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.2681813541754</v>
+        <v>26.00158794697677</v>
       </c>
       <c r="C3" t="n">
-        <v>37.16896808278424</v>
+        <v>27.04224051347839</v>
       </c>
       <c r="D3" t="n">
-        <v>91.39089378833557</v>
+        <v>81.02854677001051</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.80393786325368</v>
+        <v>45.6139618347153</v>
       </c>
       <c r="C4" t="n">
-        <v>90.28348237794518</v>
+        <v>45.0141139874205</v>
       </c>
       <c r="D4" t="n">
-        <v>144.5760939182023</v>
+        <v>126.8359129024624</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.13080309550564</v>
+        <v>67.20063035569419</v>
       </c>
       <c r="C5" t="n">
-        <v>146.9676313257475</v>
+        <v>82.63861300497527</v>
       </c>
       <c r="D5" t="n">
-        <v>129.2716289566988</v>
+        <v>106.1269268290802</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.714583126634</v>
+        <v>74.50581502299471</v>
       </c>
       <c r="C6" t="n">
-        <v>188.6192594261227</v>
+        <v>144.6241995557104</v>
       </c>
       <c r="D6" t="n">
-        <v>84.24671574453156</v>
+        <v>67.34102027740147</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43.47767883027424</v>
+        <v>62.76116723709009</v>
       </c>
       <c r="C7" t="n">
-        <v>181.456428175938</v>
+        <v>179.0609637775758</v>
       </c>
       <c r="D7" t="n">
-        <v>53.17930964364123</v>
+        <v>47.78951474732623</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.53664044579129</v>
+        <v>39.97185777840888</v>
       </c>
       <c r="C8" t="n">
-        <v>132.1825108997905</v>
+        <v>151.7094727372596</v>
       </c>
       <c r="D8" t="n">
-        <v>41.39048321104552</v>
+        <v>39.72151211382594</v>
       </c>
     </row>
     <row r="9">
@@ -1500,10 +1500,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.53437385074652</v>
+        <v>20.1906232855399</v>
       </c>
       <c r="C9" t="n">
-        <v>78.32186834940201</v>
+        <v>96.07186684218435</v>
       </c>
       <c r="D9" t="n">
         <v>36.38749691020377</v>
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.260024272905163</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>46.26486056263094</v>
+        <v>53.66723825265189</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>35.7169632282032</v>
+        <v>37.31623023842126</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1573,7 +1573,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.73397173434489</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -1587,7 +1587,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.984277800670189</v>
+        <v>7.990753310923861</v>
       </c>
       <c r="C21" t="n">
-        <v>107.7877503090476</v>
+        <v>108.8740138613376</v>
       </c>
       <c r="D21" t="n">
-        <v>9.980347250837736</v>
+        <v>9.988441638654827</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.310494316449249</v>
+        <v>8.612872609357268</v>
       </c>
       <c r="C2" t="n">
-        <v>4.076216468032757</v>
+        <v>5.158102438112742</v>
       </c>
       <c r="D2" t="n">
-        <v>38.31564940134452</v>
+        <v>19.89413547885736</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.83683425911256</v>
+        <v>31.33738671955819</v>
       </c>
       <c r="C3" t="n">
-        <v>53.46107123476006</v>
+        <v>37.30641276137879</v>
       </c>
       <c r="D3" t="n">
-        <v>100.4278814059275</v>
+        <v>88.88252840398498</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.04045694451915</v>
+        <v>32.27691927252238</v>
       </c>
       <c r="C4" t="n">
-        <v>121.0288752318425</v>
+        <v>65.88116144118645</v>
       </c>
       <c r="D4" t="n">
-        <v>141.4875156406418</v>
+        <v>120.9395361907561</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.93134408062751</v>
+        <v>41.96971435655115</v>
       </c>
       <c r="C5" t="n">
-        <v>112.7046364475339</v>
+        <v>86.41834166632549</v>
       </c>
       <c r="D5" t="n">
-        <v>83.84125394267762</v>
+        <v>68.74688298988291</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.96860943565989</v>
+        <v>38.96360288614742</v>
       </c>
       <c r="C6" t="n">
-        <v>119.50716629026</v>
+        <v>117.9373517111694</v>
       </c>
       <c r="D6" t="n">
-        <v>35.01894061048373</v>
+        <v>31.47679489356124</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.54677671800324</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="C7" t="n">
-        <v>92.94401865645402</v>
+        <v>106.6580523370777</v>
       </c>
       <c r="D7" t="n">
-        <v>29.10489244010094</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -1797,10 +1797,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.346238144429634</v>
+        <v>14.01935721664445</v>
       </c>
       <c r="C8" t="n">
-        <v>57.66295140893641</v>
+        <v>70.76437452211009</v>
       </c>
       <c r="D8" t="n">
         <v>26.78698611037422</v>
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>35.27812200440487</v>
+        <v>40.93593402397924</v>
       </c>
       <c r="D9" t="n">
         <v>27.17968519207294</v>
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>27.90126975469435</v>
+        <v>29.18245050873644</v>
       </c>
       <c r="D10" t="n">
-        <v>28.89774367450487</v>
+        <v>28.75539025738908</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>28.43141351498762</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.33774657245668</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.11386703815941</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
         <v>25.23582473766426</v>
@@ -1884,7 +1884,7 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
         <v>24.58296251434014</v>
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1915,7 +1915,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>17.9443845382232</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
         <v>6.724971774090649</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.861614631430205</v>
+        <v>5.352488483553611</v>
       </c>
       <c r="C2" t="n">
-        <v>2.899100970640831</v>
+        <v>2.526036843027043</v>
       </c>
       <c r="D2" t="n">
-        <v>27.19539315534089</v>
+        <v>13.48037772701295</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.57100161543993</v>
+        <v>31.40120032033423</v>
       </c>
       <c r="C3" t="n">
-        <v>35.35273482992764</v>
+        <v>29.14318060056657</v>
       </c>
       <c r="D3" t="n">
-        <v>106.4705385255666</v>
+        <v>86.05509501575416</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.62976760897449</v>
+        <v>44.22282533779757</v>
       </c>
       <c r="C4" t="n">
-        <v>131.2645767963198</v>
+        <v>81.37510370960962</v>
       </c>
       <c r="D4" t="n">
-        <v>157.1218478307723</v>
+        <v>134.276578752949</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.80924751240241</v>
+        <v>46.95208395560371</v>
       </c>
       <c r="C5" t="n">
-        <v>163.0192062901829</v>
+        <v>104.1634314205866</v>
       </c>
       <c r="D5" t="n">
-        <v>104.5806741948915</v>
+        <v>88.40638076742529</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.12082138754715</v>
+        <v>46.20890094348888</v>
       </c>
       <c r="C6" t="n">
-        <v>146.9587955964093</v>
+        <v>133.3134842550829</v>
       </c>
       <c r="D6" t="n">
-        <v>44.47807974090175</v>
+        <v>39.80888765950392</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.22927129890402</v>
+        <v>24.67328330313084</v>
       </c>
       <c r="C7" t="n">
-        <v>122.7076638061046</v>
+        <v>133.1279339389802</v>
       </c>
       <c r="D7" t="n">
-        <v>31.79978988825843</v>
+        <v>30.54217107911827</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.927612711792993</v>
+        <v>11.43245201595411</v>
       </c>
       <c r="C8" t="n">
-        <v>76.68922191723958</v>
+        <v>94.38031554776711</v>
       </c>
       <c r="D8" t="n">
-        <v>27.53802310412303</v>
+        <v>27.95526587842792</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.326562132615692</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>39.2718716652809</v>
+        <v>45.81718360949438</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>28.17812260729194</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2167,7 +2167,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
         <v>28.20561154301086</v>
@@ -2181,7 +2181,7 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
         <v>25.75615102091507</v>
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.12993485432585</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
         <v>5.416302084329653</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.57396255408589</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C2" t="n">
-        <v>7.711628216858696</v>
+        <v>6.252751128347935</v>
       </c>
       <c r="D2" t="n">
-        <v>25.16023016443726</v>
+        <v>14.68203691701105</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.55427084673872</v>
+        <v>24.72040719293469</v>
       </c>
       <c r="C3" t="n">
-        <v>23.10543221944868</v>
+        <v>18.96245690752714</v>
       </c>
       <c r="D3" t="n">
-        <v>103.3240371334555</v>
+        <v>78.26983572107696</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.59370498582462</v>
+        <v>52.1867627146477</v>
       </c>
       <c r="C4" t="n">
-        <v>110.0146477378976</v>
+        <v>76.93367709559706</v>
       </c>
       <c r="D4" t="n">
-        <v>171.8755523301934</v>
+        <v>144.7930601608408</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.21515128261285</v>
+        <v>56.00870652728054</v>
       </c>
       <c r="C5" t="n">
-        <v>199.9574636624692</v>
+        <v>126.5963664626262</v>
       </c>
       <c r="D5" t="n">
-        <v>131.7259982173158</v>
+        <v>111.7965198211056</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.9233512302733</v>
+        <v>54.21898046243861</v>
       </c>
       <c r="C6" t="n">
-        <v>199.0041866416455</v>
+        <v>150.219179722213</v>
       </c>
       <c r="D6" t="n">
-        <v>62.14855666964009</v>
+        <v>54.42023874180921</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.61339669317178</v>
+        <v>37.12969817461437</v>
       </c>
       <c r="C7" t="n">
-        <v>163.3107853583442</v>
+        <v>162.4723728189174</v>
       </c>
       <c r="D7" t="n">
-        <v>36.17151241526948</v>
+        <v>34.13536767666159</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.26555490623215</v>
+        <v>17.10695374650067</v>
       </c>
       <c r="C8" t="n">
-        <v>112.6555490623215</v>
+        <v>131.8487166803466</v>
       </c>
       <c r="D8" t="n">
-        <v>29.6242369756475</v>
+        <v>29.45733986592554</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>62.67968217763759</v>
+        <v>75.88124355664445</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>28.84374755077128</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>2.847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>37.15424186722054</v>
+        <v>41.56719779780995</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.46363126277853</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
         <v>28.63954402828795</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.47158305540374</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>34.9050578767911</v>
       </c>
       <c r="D19" t="n">
         <v>3.610868056219768</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.775400759905733</v>
+        <v>3.55196319396496</v>
       </c>
       <c r="C2" t="n">
-        <v>3.734568266954867</v>
+        <v>2.945243112740431</v>
       </c>
       <c r="D2" t="n">
-        <v>17.54481322259475</v>
+        <v>10.13654504634832</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.09775816426395</v>
+        <v>24.98547907308132</v>
       </c>
       <c r="C3" t="n">
-        <v>27.42021337961341</v>
+        <v>22.33476027161494</v>
       </c>
       <c r="D3" t="n">
-        <v>103.3436720875405</v>
+        <v>76.59595588533614</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.62672455487051</v>
+        <v>57.50881701936967</v>
       </c>
       <c r="C4" t="n">
-        <v>102.944100771912</v>
+        <v>74.16416682191679</v>
       </c>
       <c r="D4" t="n">
-        <v>184.5744588846258</v>
+        <v>152.9612010601743</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.12326790904115</v>
+        <v>58.48761948050374</v>
       </c>
       <c r="C5" t="n">
-        <v>236.3312161048135</v>
+        <v>149.9619618237003</v>
       </c>
       <c r="D5" t="n">
-        <v>137.8864650614645</v>
+        <v>117.8342682022234</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.39000018496002</v>
+        <v>45.08185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>225.4092728950677</v>
+        <v>186.0431534501791</v>
       </c>
       <c r="D6" t="n">
-        <v>59.53219903782235</v>
+        <v>53.05168244208915</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.425939634922873</v>
+        <v>11.31856928226148</v>
       </c>
       <c r="C7" t="n">
-        <v>161.8735067193268</v>
+        <v>171.2757044828985</v>
       </c>
       <c r="D7" t="n">
-        <v>35.75230614555609</v>
+        <v>34.19525428662065</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.75518496874405</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
-        <v>78.1912959047372</v>
+        <v>97.2175664130404</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>31.04286240828414</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>28.28906009787183</v>
+        <v>31.72812230584841</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.19120412261664</v>
+        <v>19.90198946049134</v>
       </c>
       <c r="D11" t="n">
         <v>22.92282714645877</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.97067074205961</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>29.96293993361265</v>
       </c>
       <c r="D18" t="n">
         <v>2.675262494072558</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.922662915542754</v>
+        <v>4.491495746929157</v>
       </c>
       <c r="C2" t="n">
-        <v>9.512153506447346</v>
+        <v>2.923644663247001</v>
       </c>
       <c r="D2" t="n">
-        <v>16.40794938107694</v>
+        <v>13.43030859409637</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.65396714421539</v>
+        <v>18.73665493555038</v>
       </c>
       <c r="C3" t="n">
-        <v>21.11739311834889</v>
+        <v>16.72898088036565</v>
       </c>
       <c r="D3" t="n">
-        <v>94.56193887305278</v>
+        <v>67.92221491831558</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.94655332227672</v>
+        <v>53.48856017047897</v>
       </c>
       <c r="C4" t="n">
-        <v>87.50120938410971</v>
+        <v>65.60038159777187</v>
       </c>
       <c r="D4" t="n">
-        <v>191.8747348134051</v>
+        <v>155.8455758152514</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.30890034060182</v>
+        <v>70.66129101316419</v>
       </c>
       <c r="C5" t="n">
-        <v>215.1990967709009</v>
+        <v>144.9550485320416</v>
       </c>
       <c r="D5" t="n">
-        <v>166.2589737141974</v>
+        <v>142.4515918862122</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.65417243286043</v>
+        <v>58.32464936159877</v>
       </c>
       <c r="C6" t="n">
-        <v>293.1930613870845</v>
+        <v>211.4419483067483</v>
       </c>
       <c r="D6" t="n">
-        <v>79.5372720072596</v>
+        <v>71.16492758544281</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.92983824910874</v>
+        <v>25.45180923259856</v>
       </c>
       <c r="C7" t="n">
-        <v>227.988324114124</v>
+        <v>215.2324761928452</v>
       </c>
       <c r="D7" t="n">
-        <v>41.56130731158447</v>
+        <v>39.82459562277186</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>7.009678608322226</v>
       </c>
       <c r="C8" t="n">
-        <v>130.179745583127</v>
+        <v>152.7108553955914</v>
       </c>
       <c r="D8" t="n">
-        <v>33.12907627980861</v>
+        <v>32.46148784092078</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>52.02968308196819</v>
+        <v>63.78905708343648</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>29.04009709162065</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>22.21204180858408</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3103,7 +3103,7 @@
         <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.91359050649305</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
         <v>11.82515109765283</v>
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
         <v>4.249985811684442</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.0469439633546</v>
+        <v>3.205406254365836</v>
       </c>
       <c r="C2" t="n">
-        <v>5.37408693304704</v>
+        <v>2.122538536581604</v>
       </c>
       <c r="D2" t="n">
-        <v>11.81926061142735</v>
+        <v>10.32798584867644</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.45976102522377</v>
+        <v>17.48001787411446</v>
       </c>
       <c r="C3" t="n">
-        <v>28.14179794223482</v>
+        <v>14.52986602285279</v>
       </c>
       <c r="D3" t="n">
-        <v>88.16585257988481</v>
+        <v>64.13266877992288</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.97734735400687</v>
+        <v>47.94953962311847</v>
       </c>
       <c r="C4" t="n">
-        <v>75.68293052038661</v>
+        <v>56.99830821316132</v>
       </c>
       <c r="D4" t="n">
-        <v>194.6187196467749</v>
+        <v>155.3861178896639</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.89857085795565</v>
+        <v>76.30634031258334</v>
       </c>
       <c r="C5" t="n">
-        <v>201.1355609075653</v>
+        <v>139.2363681548039</v>
       </c>
       <c r="D5" t="n">
-        <v>185.7957530287089</v>
+        <v>158.9694970101648</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.41645061971246</v>
+        <v>69.43410638285567</v>
       </c>
       <c r="C6" t="n">
-        <v>322.8585317663104</v>
+        <v>228.6294053649972</v>
       </c>
       <c r="D6" t="n">
-        <v>94.95365620704727</v>
+        <v>85.73602701187396</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.13323995033708</v>
+        <v>23.83487076370406</v>
       </c>
       <c r="C7" t="n">
-        <v>290.4500583014188</v>
+        <v>255.1768450355352</v>
       </c>
       <c r="D7" t="n">
-        <v>46.77144237802229</v>
+        <v>44.91495746929157</v>
       </c>
     </row>
     <row r="8">
@@ -3352,10 +3352,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>169.984706251814</v>
+        <v>192.5158160642783</v>
       </c>
       <c r="D8" t="n">
         <v>34.38080460272329</v>
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>57.79843259212245</v>
+        <v>76.87968097186344</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.0343454741154</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>19.52696183746906</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.290818304635308</v>
+        <v>6.104507225006667</v>
       </c>
       <c r="C2" t="n">
-        <v>10.89838126484384</v>
+        <v>5.011822030179967</v>
       </c>
       <c r="D2" t="n">
-        <v>19.44645852572082</v>
+        <v>17.01172421918873</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.43106935762236</v>
+        <v>14.25006792714245</v>
       </c>
       <c r="C3" t="n">
-        <v>24.69586350032851</v>
+        <v>11.57480543306989</v>
       </c>
       <c r="D3" t="n">
-        <v>79.40375431948202</v>
+        <v>58.93922342445726</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.04268248183489</v>
+        <v>41.28739970209961</v>
       </c>
       <c r="C4" t="n">
-        <v>73.09209832887927</v>
+        <v>47.50284441768617</v>
       </c>
       <c r="D4" t="n">
-        <v>193.3424476312541</v>
+        <v>150.804301353944</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.7758523949248</v>
+        <v>74.63736921536378</v>
       </c>
       <c r="C5" t="n">
-        <v>175.5855769045421</v>
+        <v>124.0929098167969</v>
       </c>
       <c r="D5" t="n">
-        <v>201.8718716857504</v>
+        <v>174.2602175038089</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.84162949110934</v>
+        <v>82.51589454194442</v>
       </c>
       <c r="C6" t="n">
-        <v>322.8182801104363</v>
+        <v>226.536319259543</v>
       </c>
       <c r="D6" t="n">
-        <v>119.9096828490012</v>
+        <v>108.1159476778843</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.94897448157494</v>
+        <v>43.95677170994669</v>
       </c>
       <c r="C7" t="n">
-        <v>357.2835150157247</v>
+        <v>287.5156144134251</v>
       </c>
       <c r="D7" t="n">
-        <v>57.3713723407751</v>
+        <v>54.97590794241288</v>
       </c>
     </row>
     <row r="8">
@@ -3663,10 +3663,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.093127163183205</v>
+        <v>12.01659189998096</v>
       </c>
       <c r="C8" t="n">
-        <v>249.7615246989098</v>
+        <v>253.4332611127928</v>
       </c>
       <c r="D8" t="n">
         <v>37.30150402285756</v>
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>109.3843657117711</v>
+        <v>137.2296758473234</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>41.99425804915732</v>
+        <v>52.24370408149402</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>26.76244241776806</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>25.76596849795753</v>
+        <v>27.72062817711293</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.87606310955342</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>11.98419422574081</v>
+      </c>
+      <c r="D14" t="n">
         <v>11.36962016288231</v>
-      </c>
-      <c r="D14" t="n">
-        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.45221014322606</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.409028939772425</v>
+        <v>9.727156253677396</v>
       </c>
       <c r="C2" t="n">
-        <v>5.549819772107219</v>
+        <v>7.407286428542184</v>
       </c>
       <c r="D2" t="n">
-        <v>19.71545739668445</v>
+        <v>8.455792976677778</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.405281875404686</v>
+        <v>4.319689898685966</v>
       </c>
       <c r="C2" t="n">
-        <v>6.451064164605791</v>
+        <v>2.806816686441631</v>
       </c>
       <c r="D2" t="n">
-        <v>14.46899766518949</v>
+        <v>12.52022847225957</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.40223882130071</v>
+        <v>20.07674055184727</v>
       </c>
       <c r="C3" t="n">
-        <v>33.41378311404019</v>
+        <v>15.79141182280995</v>
       </c>
       <c r="D3" t="n">
-        <v>87.38045441648735</v>
+        <v>65.91944960165209</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.36321525950487</v>
+        <v>56.57713844803943</v>
       </c>
       <c r="C4" t="n">
-        <v>105.0754750378319</v>
+        <v>68.26779011021046</v>
       </c>
       <c r="D4" t="n">
-        <v>195.9460425429166</v>
+        <v>155.513745091216</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.10944132572369</v>
+        <v>49.23464736797755</v>
       </c>
       <c r="C5" t="n">
-        <v>269.6615506639927</v>
+        <v>189.133695223148</v>
       </c>
       <c r="D5" t="n">
-        <v>181.8687622117216</v>
+        <v>159.435827169682</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.70443718775948</v>
+        <v>27.29062268265284</v>
       </c>
       <c r="C6" t="n">
-        <v>289.0873924879243</v>
+        <v>235.9954583899611</v>
       </c>
       <c r="D6" t="n">
-        <v>90.80773565201298</v>
+        <v>84.44797402390215</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.671155576806323</v>
+        <v>7.964919124554372</v>
       </c>
       <c r="C7" t="n">
-        <v>175.6474270099096</v>
+        <v>178.222551238149</v>
       </c>
       <c r="D7" t="n">
-        <v>32.93763547748049</v>
+        <v>33.23706852727577</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.50207398749762</v>
+        <v>1.919316761802514</v>
       </c>
       <c r="C8" t="n">
-        <v>80.6113039957056</v>
+        <v>101.1396484915064</v>
       </c>
       <c r="D8" t="n">
-        <v>24.28352946454485</v>
+        <v>24.78422079371073</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>32.06093477758807</v>
+        <v>39.82655911818034</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>20.41249826669968</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.21418523044183</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>19.07535789351553</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.10418842983717</v>
+        <v>16.17036643664921</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>16.52575910558656</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>9.886199381765381</v>
+      </c>
+      <c r="D13" t="n">
         <v>9.365873098514571</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.721044783273664</v>
+        <v>8.222137023067036</v>
       </c>
       <c r="C2" t="n">
-        <v>4.211697651218817</v>
+        <v>6.042657119639118</v>
       </c>
       <c r="D2" t="n">
-        <v>19.72822011683965</v>
+        <v>18.4980902434184</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.370781837035805</v>
+        <v>20.64615422031042</v>
       </c>
       <c r="C3" t="n">
-        <v>13.98499604699582</v>
+        <v>18.66302385773187</v>
       </c>
       <c r="D3" t="n">
-        <v>19.69876768571225</v>
+        <v>10.23962855529423</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4571,7 +4571,7 @@
         <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
         <v>32.8453511932813</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39690921336726</v>
+        <v>13.39760897911447</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13675999939329</v>
+        <v>70.14042347889342</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576106966278501</v>
+        <v>1.576189291660526</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.340306600475149</v>
+        <v>5.543929285881738</v>
       </c>
       <c r="C2" t="n">
-        <v>8.552004251693965</v>
+        <v>9.075275778057515</v>
       </c>
       <c r="D2" t="n">
-        <v>33.12318579358313</v>
+        <v>17.87468045122167</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.62237129123025</v>
+        <v>25.38799563182252</v>
       </c>
       <c r="C3" t="n">
-        <v>15.5116137270996</v>
+        <v>21.73098543350315</v>
       </c>
       <c r="D3" t="n">
-        <v>31.50919256780138</v>
+        <v>23.30178176029805</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.01422749394496</v>
+        <v>23.75142220884308</v>
       </c>
       <c r="C4" t="n">
-        <v>21.87530234602743</v>
+        <v>28.99690019263379</v>
       </c>
       <c r="D4" t="n">
-        <v>25.39781310886498</v>
+        <v>20.43311496848886</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.424156065963628</v>
+        <v>5.473243451175969</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4882,7 +4882,7 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
         <v>34.57617239586842</v>
@@ -4896,7 +4896,7 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43899466816121</v>
+        <v>15.43814021436994</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13333867500465</v>
+        <v>86.12857172227444</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250314666981307</v>
+        <v>3.25013478197262</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.802128932098649</v>
+        <v>7.067601722872788</v>
       </c>
       <c r="C2" t="n">
-        <v>8.84260157215102</v>
+        <v>8.06113039957056</v>
       </c>
       <c r="D2" t="n">
-        <v>43.98916938418684</v>
+        <v>29.03027961457818</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.1595672119025</v>
+        <v>21.89297380470387</v>
       </c>
       <c r="C3" t="n">
-        <v>26.28629478120835</v>
+        <v>29.81567777797563</v>
       </c>
       <c r="D3" t="n">
-        <v>50.69745144730529</v>
+        <v>32.19150722225291</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.09601565303371</v>
+        <v>38.27539774547039</v>
       </c>
       <c r="C4" t="n">
-        <v>31.86851222755571</v>
+        <v>43.41877396801944</v>
       </c>
       <c r="D4" t="n">
-        <v>35.46759931132452</v>
+        <v>27.5164246546296</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.989282890711298</v>
+        <v>19.8067599331794</v>
       </c>
       <c r="C5" t="n">
-        <v>25.35363446217388</v>
+        <v>32.86400439966199</v>
       </c>
       <c r="D5" t="n">
-        <v>31.75953823238432</v>
+        <v>30.01693605734623</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
         <v>36.54850353370026</v>
@@ -5207,7 +5207,7 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.13430381349934</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
         <v>37.4890178343687</v>
@@ -5218,10 +5218,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.51451791248334</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.79113408536946</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
         <v>37.88564390688441</v>
@@ -5263,7 +5263,7 @@
         <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>31.67707142522758</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72976520309945</v>
+        <v>16.72750878837972</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0515677389066</v>
+        <v>102.0378036091163</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182441300774863</v>
+        <v>4.18187719709493</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.720643872646163</v>
+        <v>7.716536955379929</v>
       </c>
       <c r="C2" t="n">
-        <v>10.41143440353742</v>
+        <v>6.302820261264523</v>
       </c>
       <c r="D2" t="n">
-        <v>34.44069121268235</v>
+        <v>35.28499423833461</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.10833640483242</v>
+        <v>23.07597978832128</v>
       </c>
       <c r="C3" t="n">
-        <v>30.80724295926491</v>
+        <v>30.61089341841555</v>
       </c>
       <c r="D3" t="n">
-        <v>72.85058839363457</v>
+        <v>47.0944373727195</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.74615361742335</v>
+        <v>40.24085664937251</v>
       </c>
       <c r="C4" t="n">
-        <v>50.15749020996954</v>
+        <v>60.099649210877</v>
       </c>
       <c r="D4" t="n">
-        <v>51.95703375185395</v>
+        <v>36.92254940901829</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.0219836645877</v>
+        <v>38.63177216211199</v>
       </c>
       <c r="C5" t="n">
-        <v>43.44233591292137</v>
+        <v>58.41398840268523</v>
       </c>
       <c r="D5" t="n">
-        <v>36.76645152404306</v>
+        <v>32.7658296292373</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.700649065662736</v>
+        <v>16.06041069377357</v>
       </c>
       <c r="C6" t="n">
-        <v>26.76735115628929</v>
+        <v>32.88560284915541</v>
       </c>
       <c r="D6" t="n">
-        <v>38.7220929509027</v>
+        <v>38.19882142453915</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>21.08008670558751</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.62700229231099</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5546,7 +5546,7 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
         <v>42.15624642035802</v>
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04881896788962</v>
+        <v>18.04444758726981</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7470570762323</v>
+        <v>117.7185390217125</v>
       </c>
       <c r="D21" t="n">
-        <v>6.016272989296541</v>
+        <v>6.014815862423268</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.339545836949155</v>
+        <v>8.247662463377454</v>
       </c>
       <c r="C2" t="n">
-        <v>8.205447312094842</v>
+        <v>3.7394770054761</v>
       </c>
       <c r="D2" t="n">
-        <v>30.10823859384118</v>
+        <v>37.50767104074939</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.98914402199105</v>
+        <v>22.07950586851076</v>
       </c>
       <c r="C3" t="n">
-        <v>33.98319678250334</v>
+        <v>25.46653544816226</v>
       </c>
       <c r="D3" t="n">
-        <v>77.92131528606934</v>
+        <v>59.67553420264237</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.8707945181337</v>
+        <v>30.70710469343173</v>
       </c>
       <c r="C4" t="n">
-        <v>53.92249265575607</v>
+        <v>57.80235958293945</v>
       </c>
       <c r="D4" t="n">
-        <v>65.88116144118645</v>
+        <v>44.860961345558</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.68404147014855</v>
+        <v>30.40963513904496</v>
       </c>
       <c r="C5" t="n">
-        <v>51.86082247683777</v>
+        <v>63.49453277216247</v>
       </c>
       <c r="D5" t="n">
-        <v>37.40458753180348</v>
+        <v>31.07231483941155</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.14970867713103</v>
+        <v>18.31450342272425</v>
       </c>
       <c r="C6" t="n">
-        <v>32.80509953740717</v>
+        <v>43.06927178530758</v>
       </c>
       <c r="D6" t="n">
-        <v>32.24157635516951</v>
+        <v>30.67176177607885</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.030475236560656</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>19.04394196697963</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D7" t="n">
-        <v>30.84160412891355</v>
+        <v>31.26081039862693</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.06830573313655</v>
       </c>
       <c r="D10" t="n">
         <v>33.16834618797849</v>
@@ -5882,10 +5882,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.553926689373453</v>
+        <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
         <v>34.65078522139116</v>
@@ -5896,7 +5896,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
         <v>19.7439280801076</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>29.49955501720816</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.051033963376302</v>
+        <v>7.0475238666185</v>
       </c>
       <c r="C21" t="n">
-        <v>66.10344340665283</v>
+        <v>66.07053624954844</v>
       </c>
       <c r="D21" t="n">
-        <v>4.406896227110188</v>
+        <v>4.404702416636563</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.719662124941918</v>
+        <v>8.216246536841556</v>
       </c>
       <c r="C2" t="n">
-        <v>10.28871594050657</v>
+        <v>2.322815068247953</v>
       </c>
       <c r="D2" t="n">
-        <v>25.56667371399543</v>
+        <v>26.9627189494344</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.21204180858409</v>
+        <v>26.18321127226244</v>
       </c>
       <c r="C3" t="n">
-        <v>32.74619467515236</v>
+        <v>18.55994034878595</v>
       </c>
       <c r="D3" t="n">
-        <v>84.38612391853459</v>
+        <v>76.7628529950581</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.3032054763588</v>
+        <v>38.50512670826415</v>
       </c>
       <c r="C4" t="n">
-        <v>73.28353913120742</v>
+        <v>61.6056501891916</v>
       </c>
       <c r="D4" t="n">
-        <v>91.43212719191393</v>
+        <v>65.72800879932396</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.00435326364027</v>
+        <v>39.76078202199582</v>
       </c>
       <c r="C5" t="n">
-        <v>80.62603021126931</v>
+        <v>89.60902170512763</v>
       </c>
       <c r="D5" t="n">
-        <v>53.03891972193394</v>
+        <v>40.42346172236243</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.04532462531138</v>
+        <v>31.07427833482005</v>
       </c>
       <c r="C6" t="n">
-        <v>61.14226527278711</v>
+        <v>76.51839781670066</v>
       </c>
       <c r="D6" t="n">
-        <v>37.35353665118265</v>
+        <v>34.09315252537899</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.701630813366979</v>
+        <v>15.27108553955913</v>
       </c>
       <c r="C7" t="n">
-        <v>35.63253292563798</v>
+        <v>44.79518424937346</v>
       </c>
       <c r="D7" t="n">
-        <v>33.71616140694821</v>
+        <v>33.59638818703009</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="C8" t="n">
-        <v>22.78145547704723</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D8" t="n">
-        <v>31.71045084717197</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
         <v>33.1958351236974</v>
@@ -6221,7 +6221,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
         <v>20.81305133003238</v>
@@ -6238,7 +6238,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.268450137284244</v>
+        <v>7.263933477925113</v>
       </c>
       <c r="C21" t="n">
-        <v>75.41017017432404</v>
+        <v>75.36330983347307</v>
       </c>
       <c r="D21" t="n">
-        <v>5.451337602963183</v>
+        <v>5.447950108443835</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.007895039362979</v>
+        <v>6.662139921018856</v>
       </c>
       <c r="C2" t="n">
-        <v>9.13221714490383</v>
+        <v>5.528221322613789</v>
       </c>
       <c r="D2" t="n">
-        <v>26.34029090494192</v>
+        <v>23.14764737073129</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.81796006855362</v>
+        <v>27.37112599440108</v>
       </c>
       <c r="C3" t="n">
-        <v>36.97261854193488</v>
+        <v>12.95416095753666</v>
       </c>
       <c r="D3" t="n">
-        <v>85.04880361890119</v>
+        <v>80.179335005837</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.088464771036</v>
+        <v>45.55014823393926</v>
       </c>
       <c r="C4" t="n">
-        <v>77.53352494289186</v>
+        <v>52.41649167744146</v>
       </c>
       <c r="D4" t="n">
-        <v>111.1122416712455</v>
+        <v>87.51397210426492</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.30012136452582</v>
+        <v>49.21010367537139</v>
       </c>
       <c r="C5" t="n">
-        <v>111.3547333541945</v>
+        <v>103.2553147941583</v>
       </c>
       <c r="D5" t="n">
-        <v>73.80288366675398</v>
+        <v>54.85515297479054</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.62521872335175</v>
+        <v>43.47178834404877</v>
       </c>
       <c r="C6" t="n">
-        <v>97.28825224774619</v>
+        <v>112.1411132652962</v>
       </c>
       <c r="D6" t="n">
-        <v>45.04160292313942</v>
+        <v>38.84284791852506</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.00779722837174</v>
+        <v>26.52976821186155</v>
       </c>
       <c r="C7" t="n">
-        <v>63.4199199466397</v>
+        <v>79.46953141566655</v>
       </c>
       <c r="D7" t="n">
-        <v>37.18958478457343</v>
+        <v>36.23139902522853</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>11.76624623539802</v>
       </c>
       <c r="C8" t="n">
-        <v>36.13322425480386</v>
+        <v>43.64359419229195</v>
       </c>
       <c r="D8" t="n">
-        <v>33.88011327355743</v>
+        <v>33.12907627980861</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>26.5140602485936</v>
+        <v>27.95624762613216</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
         <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6521,7 +6521,7 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
         <v>34.28066633689012</v>
@@ -6535,7 +6535,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
         <v>31.47974013667398</v>
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.471666778876633</v>
+        <v>7.467167410064114</v>
       </c>
       <c r="C21" t="n">
-        <v>84.05625126236212</v>
+        <v>84.00563336322129</v>
       </c>
       <c r="D21" t="n">
-        <v>6.537708431517053</v>
+        <v>6.5337714838061</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_57_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_57_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497640384105</v>
+        <v>10.84497627946917</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907219148862</v>
+        <v>37.78907175811766</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.927211801165494</v>
+        <v>7.782314051564466</v>
       </c>
       <c r="C2" t="n">
-        <v>5.667629496616836</v>
+        <v>5.899321954819084</v>
       </c>
       <c r="D2" t="n">
-        <v>22.90908267859932</v>
+        <v>30.71004993654448</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.78422079371073</v>
+        <v>22.25131171675396</v>
       </c>
       <c r="C3" t="n">
-        <v>17.56346642897544</v>
+        <v>20.18473279931442</v>
       </c>
       <c r="D3" t="n">
-        <v>79.78172718561706</v>
+        <v>85.21570072862315</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.79187915336223</v>
+        <v>42.72958707963818</v>
       </c>
       <c r="C4" t="n">
-        <v>41.78514578815274</v>
+        <v>66.77455185205106</v>
       </c>
       <c r="D4" t="n">
-        <v>105.7518992060579</v>
+        <v>107.0154085014236</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.90486225480863</v>
+        <v>53.33344403320799</v>
       </c>
       <c r="C5" t="n">
-        <v>98.91108120286617</v>
+        <v>97.58572180213298</v>
       </c>
       <c r="D5" t="n">
-        <v>71.15216486528759</v>
+        <v>76.23270923476484</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.66174867705392</v>
+        <v>50.39507315439728</v>
       </c>
       <c r="C6" t="n">
-        <v>138.425444551096</v>
+        <v>102.5209675113817</v>
       </c>
       <c r="D6" t="n">
-        <v>46.65166915810419</v>
+        <v>48.74475526355839</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.80652325346792</v>
+        <v>36.17151241526948</v>
       </c>
       <c r="C7" t="n">
-        <v>119.7133333081518</v>
+        <v>93.00390526641308</v>
       </c>
       <c r="D7" t="n">
-        <v>38.86640986342697</v>
+        <v>39.58504918293564</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.11110172149591</v>
+        <v>18.19178495969339</v>
       </c>
       <c r="C8" t="n">
-        <v>74.51955949085414</v>
+        <v>60.91744504851459</v>
       </c>
       <c r="D8" t="n">
-        <v>35.46563581591602</v>
+        <v>35.549084370777</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.38749691020377</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -895,7 +895,7 @@
         <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>29.60951076008381</v>
       </c>
       <c r="D10" t="n">
         <v>34.73423377625215</v>
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>22.73924032576462</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.656393479920259</v>
+        <v>7.680683395993269</v>
       </c>
       <c r="C21" t="n">
-        <v>92.83377094403313</v>
+        <v>93.12828617641837</v>
       </c>
       <c r="D21" t="n">
-        <v>7.656393479920259</v>
+        <v>8.640768820492427</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.931940613237481</v>
+        <v>8.647233779005905</v>
       </c>
       <c r="C2" t="n">
-        <v>9.141052874242051</v>
+        <v>9.460120878122265</v>
       </c>
       <c r="D2" t="n">
-        <v>27.42021337961341</v>
+        <v>30.9790488075081</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.81719930502762</v>
+        <v>23.94482650657971</v>
       </c>
       <c r="C3" t="n">
-        <v>19.70367642423349</v>
+        <v>21.48554850744145</v>
       </c>
       <c r="D3" t="n">
-        <v>79.14359117785662</v>
+        <v>88.77944489503906</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.86020058203201</v>
+        <v>42.04040019125691</v>
       </c>
       <c r="C4" t="n">
-        <v>42.72958707963818</v>
+        <v>58.51707191163113</v>
       </c>
       <c r="D4" t="n">
-        <v>119.1272299287165</v>
+        <v>122.4455371690707</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64.91806694332035</v>
+        <v>58.04583301359268</v>
       </c>
       <c r="C5" t="n">
-        <v>87.52280783360315</v>
+        <v>108.8021893231528</v>
       </c>
       <c r="D5" t="n">
-        <v>88.60273030827464</v>
+        <v>93.06968236259763</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>65.73095404243671</v>
+        <v>60.82025202579416</v>
       </c>
       <c r="C6" t="n">
-        <v>147.5625704345211</v>
+        <v>127.4367424974615</v>
       </c>
       <c r="D6" t="n">
-        <v>56.75483478250812</v>
+        <v>59.77370897306707</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>51.08327829507428</v>
+        <v>47.01098881785852</v>
       </c>
       <c r="C7" t="n">
-        <v>155.6452992835851</v>
+        <v>118.2760546691345</v>
       </c>
       <c r="D7" t="n">
-        <v>42.51949307092936</v>
+        <v>43.59745205019235</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.70768553050848</v>
+        <v>27.62147165898401</v>
       </c>
       <c r="C8" t="n">
-        <v>113.3231375012093</v>
+        <v>90.45823346930109</v>
       </c>
       <c r="D8" t="n">
-        <v>37.80219535202343</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.86718632248619</v>
+        <v>12.86874890726719</v>
       </c>
       <c r="C9" t="n">
-        <v>63.89999457401638</v>
+        <v>54.35937038414588</v>
       </c>
       <c r="D9" t="n">
-        <v>34.83437204208531</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>39.00483628972578</v>
+        <v>36.44247478164161</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1217,7 +1217,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
         <v>31.98534020436108</v>
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.72437524148068</v>
+        <v>30.59224021203486</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
         <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.831115815995572</v>
+        <v>7.859907356215337</v>
       </c>
       <c r="C21" t="n">
-        <v>100.825616130943</v>
+        <v>101.1963072112725</v>
       </c>
       <c r="D21" t="n">
-        <v>8.810005292995019</v>
+        <v>9.824884195269172</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.310895227076751</v>
+        <v>9.172468800777949</v>
       </c>
       <c r="C2" t="n">
-        <v>7.498588965037137</v>
+        <v>9.84005723966578</v>
       </c>
       <c r="D2" t="n">
-        <v>23.89573912136737</v>
+        <v>29.78720709455247</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.00158794697677</v>
+        <v>25.79051219056371</v>
       </c>
       <c r="C3" t="n">
-        <v>27.04224051347839</v>
+        <v>28.37250865273282</v>
       </c>
       <c r="D3" t="n">
-        <v>81.02854677001051</v>
+        <v>91.02764713776426</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.6139618347153</v>
+        <v>42.71682435948296</v>
       </c>
       <c r="C4" t="n">
-        <v>45.0141139874205</v>
+        <v>55.58164627593317</v>
       </c>
       <c r="D4" t="n">
-        <v>126.8359129024624</v>
+        <v>133.1534593792906</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>67.20063035569419</v>
+        <v>60.32839642596651</v>
       </c>
       <c r="C5" t="n">
-        <v>82.63861300497527</v>
+        <v>107.0595871481147</v>
       </c>
       <c r="D5" t="n">
-        <v>106.1269268290802</v>
+        <v>110.7411410390402</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>74.50581502299471</v>
+        <v>67.86429180376503</v>
       </c>
       <c r="C6" t="n">
-        <v>144.6241995557104</v>
+        <v>147.3210604992764</v>
       </c>
       <c r="D6" t="n">
-        <v>67.34102027740147</v>
+        <v>70.88316599432396</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>62.76116723709009</v>
+        <v>57.49114556069321</v>
       </c>
       <c r="C7" t="n">
-        <v>179.0609637775758</v>
+        <v>145.7041220303819</v>
       </c>
       <c r="D7" t="n">
-        <v>47.78951474732623</v>
+        <v>48.92736033654828</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>39.97185777840888</v>
+        <v>37.30150402285756</v>
       </c>
       <c r="C8" t="n">
-        <v>151.7094727372596</v>
+        <v>118.663845012312</v>
       </c>
       <c r="D8" t="n">
-        <v>39.72151211382594</v>
+        <v>40.72289477215769</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20.1906232855399</v>
+        <v>18.97031088916111</v>
       </c>
       <c r="C9" t="n">
-        <v>96.07186684218435</v>
+        <v>79.43124325520091</v>
       </c>
       <c r="D9" t="n">
-        <v>36.38749691020377</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.110618695410402</v>
       </c>
       <c r="C10" t="n">
-        <v>53.66723825265189</v>
+        <v>48.11545498513618</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
-        <v>37.31623023842126</v>
+        <v>36.60544490054656</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.76190263842031</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.65056423721292</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.990753310923861</v>
+        <v>8.023669328270234</v>
       </c>
       <c r="C21" t="n">
-        <v>108.8740138613376</v>
+        <v>109.3224945976819</v>
       </c>
       <c r="D21" t="n">
-        <v>9.988441638654827</v>
+        <v>11.03254532637157</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.612872609357268</v>
+        <v>8.492117641734909</v>
       </c>
       <c r="C2" t="n">
-        <v>5.158102438112742</v>
+        <v>6.690610604442013</v>
       </c>
       <c r="D2" t="n">
-        <v>19.89413547885736</v>
+        <v>24.52798464290231</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>31.33738671955819</v>
+        <v>30.25746424488669</v>
       </c>
       <c r="C3" t="n">
-        <v>37.30641276137879</v>
+        <v>41.96480561802991</v>
       </c>
       <c r="D3" t="n">
-        <v>88.88252840398498</v>
+        <v>99.62284828844508</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.27691927252238</v>
+        <v>28.98413747247858</v>
       </c>
       <c r="C4" t="n">
-        <v>65.88116144118645</v>
+        <v>83.85107141972007</v>
       </c>
       <c r="D4" t="n">
-        <v>120.9395361907561</v>
+        <v>126.7210484210655</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.96971435655115</v>
+        <v>38.2145293878071</v>
       </c>
       <c r="C5" t="n">
-        <v>86.41834166632549</v>
+        <v>88.01368168572657</v>
       </c>
       <c r="D5" t="n">
-        <v>68.74688298988291</v>
+        <v>72.10936887692823</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.96360288614742</v>
+        <v>35.70321876034376</v>
       </c>
       <c r="C6" t="n">
-        <v>117.9373517111694</v>
+        <v>95.95994760390025</v>
       </c>
       <c r="D6" t="n">
-        <v>31.47679489356124</v>
+        <v>32.20132469929539</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.4698816019025</v>
+        <v>24.73316991308989</v>
       </c>
       <c r="C7" t="n">
-        <v>106.6580523370777</v>
+        <v>83.42204767296421</v>
       </c>
       <c r="D7" t="n">
-        <v>27.90716024091983</v>
+        <v>28.62579956042849</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.01935721664445</v>
+        <v>13.18487166803466</v>
       </c>
       <c r="C8" t="n">
-        <v>70.76437452211009</v>
+        <v>58.4974369575462</v>
       </c>
       <c r="D8" t="n">
-        <v>26.78698611037422</v>
+        <v>26.8704346652352</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>6.545311944213482</v>
       </c>
       <c r="C9" t="n">
-        <v>40.93593402397924</v>
+        <v>36.72030938194344</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>27.73437264497238</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>29.18245050873644</v>
+        <v>28.61303684027329</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>28.47068342315751</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>26.68684784454105</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1971,7 +1971,7 @@
         <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.352488483553611</v>
+        <v>5.250386722311942</v>
       </c>
       <c r="C2" t="n">
-        <v>2.526036843027043</v>
+        <v>2.969786805346601</v>
       </c>
       <c r="D2" t="n">
-        <v>13.48037772701295</v>
+        <v>16.91158595335556</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>31.40120032033423</v>
+        <v>30.60107594137308</v>
       </c>
       <c r="C3" t="n">
-        <v>29.14318060056657</v>
+        <v>34.45934441906304</v>
       </c>
       <c r="D3" t="n">
-        <v>86.05509501575416</v>
+        <v>97.01139939514857</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.22282533779757</v>
+        <v>41.30016242225481</v>
       </c>
       <c r="C4" t="n">
-        <v>81.37510370960962</v>
+        <v>97.2008767020682</v>
       </c>
       <c r="D4" t="n">
-        <v>134.276578752949</v>
+        <v>145.6226369709294</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.95208395560371</v>
+        <v>42.21515128261285</v>
       </c>
       <c r="C5" t="n">
-        <v>104.1634314205866</v>
+        <v>120.6322491593268</v>
       </c>
       <c r="D5" t="n">
-        <v>88.40638076742529</v>
+        <v>92.70152697350508</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.20890094348888</v>
+        <v>42.74725853831463</v>
       </c>
       <c r="C6" t="n">
-        <v>133.3134842550829</v>
+        <v>117.5750868083023</v>
       </c>
       <c r="D6" t="n">
-        <v>39.80888765950392</v>
+        <v>41.0164373357275</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.67328330313084</v>
+        <v>23.29589127407256</v>
       </c>
       <c r="C7" t="n">
-        <v>133.1279339389802</v>
+        <v>107.0173719968321</v>
       </c>
       <c r="D7" t="n">
-        <v>30.54217107911827</v>
+        <v>31.32069700858599</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.43245201595411</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>94.38031554776711</v>
+        <v>76.2719791429347</v>
       </c>
       <c r="D8" t="n">
-        <v>27.95526587842792</v>
+        <v>28.12216298814988</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>45.81718360949438</v>
+        <v>42.59999638267758</v>
       </c>
       <c r="D9" t="n">
-        <v>28.17812260729194</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
         <v>29.89421759431538</v>
@@ -2150,10 +2150,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>29.67528785626833</v>
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2268,7 +2268,7 @@
         <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.9248473951295</v>
+        <v>6.405903770210438</v>
       </c>
       <c r="C2" t="n">
-        <v>6.252751128347935</v>
+        <v>4.787001805907448</v>
       </c>
       <c r="D2" t="n">
-        <v>14.68203691701105</v>
+        <v>14.35118794067987</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.72040719293469</v>
+        <v>24.15099352447153</v>
       </c>
       <c r="C3" t="n">
-        <v>18.96245690752714</v>
+        <v>22.38384765682728</v>
       </c>
       <c r="D3" t="n">
-        <v>78.26983572107696</v>
+        <v>89.47157702653307</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>52.1867627146477</v>
+        <v>49.92776124717579</v>
       </c>
       <c r="C4" t="n">
-        <v>76.93367709559706</v>
+        <v>91.44488991206916</v>
       </c>
       <c r="D4" t="n">
-        <v>144.7930601608408</v>
+        <v>158.5895606486212</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.00870652728054</v>
+        <v>51.3454049321082</v>
       </c>
       <c r="C5" t="n">
-        <v>126.5963664626262</v>
+        <v>149.2992821233337</v>
       </c>
       <c r="D5" t="n">
-        <v>111.7965198211056</v>
+        <v>118.6442100582271</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.21898046243861</v>
+        <v>49.46928506929254</v>
       </c>
       <c r="C6" t="n">
-        <v>150.219179722213</v>
+        <v>153.7613254391355</v>
       </c>
       <c r="D6" t="n">
-        <v>54.42023874180921</v>
+        <v>56.43282153551517</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.12969817461437</v>
+        <v>34.6743471662931</v>
       </c>
       <c r="C7" t="n">
-        <v>162.4723728189174</v>
+        <v>137.260110026155</v>
       </c>
       <c r="D7" t="n">
-        <v>34.13536767666159</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.10695374650067</v>
+        <v>16.1890196430299</v>
       </c>
       <c r="C8" t="n">
-        <v>131.8487166803466</v>
+        <v>106.2300103380261</v>
       </c>
       <c r="D8" t="n">
-        <v>29.45733986592554</v>
+        <v>29.79113408536946</v>
       </c>
     </row>
     <row r="9">
@@ -2436,10 +2436,10 @@
         <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>75.88124355664445</v>
+        <v>64.78749449865549</v>
       </c>
       <c r="D9" t="n">
-        <v>28.84374755077128</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>41.56719779780995</v>
+        <v>40.00131020953629</v>
       </c>
       <c r="D10" t="n">
-        <v>30.46363126277853</v>
+        <v>30.60598467989432</v>
       </c>
     </row>
     <row r="11">
@@ -2461,7 +2461,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
         <v>32.69612554223576</v>
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2579,7 +2579,7 @@
         <v>34.9050578767911</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.55196319396496</v>
+        <v>3.806235849364884</v>
       </c>
       <c r="C2" t="n">
-        <v>2.945243112740431</v>
+        <v>2.270782439922872</v>
       </c>
       <c r="D2" t="n">
-        <v>10.13654504634832</v>
+        <v>9.918597056005526</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.98547907308132</v>
+        <v>25.12292375167588</v>
       </c>
       <c r="C3" t="n">
-        <v>22.33476027161494</v>
+        <v>22.00587479069226</v>
       </c>
       <c r="D3" t="n">
-        <v>76.59595588533614</v>
+        <v>86.19744843286996</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>57.50881701936967</v>
+        <v>54.95627298832795</v>
       </c>
       <c r="C4" t="n">
-        <v>74.16416682191679</v>
+        <v>88.02448091047326</v>
       </c>
       <c r="D4" t="n">
-        <v>152.9612010601743</v>
+        <v>168.365804287511</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.48761948050374</v>
+        <v>53.55433726666352</v>
       </c>
       <c r="C5" t="n">
-        <v>149.9619618237003</v>
+        <v>176.444606145758</v>
       </c>
       <c r="D5" t="n">
-        <v>117.8342682022234</v>
+        <v>125.2464633692869</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.08185457901354</v>
+        <v>41.62021217383928</v>
       </c>
       <c r="C6" t="n">
-        <v>186.0431534501791</v>
+        <v>186.1639084178015</v>
       </c>
       <c r="D6" t="n">
-        <v>53.05168244208915</v>
+        <v>54.98376192404687</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.31856928226148</v>
+        <v>10.71970318267092</v>
       </c>
       <c r="C7" t="n">
-        <v>171.2757044828985</v>
+        <v>142.2306986527566</v>
       </c>
       <c r="D7" t="n">
-        <v>34.19525428662065</v>
+        <v>34.91389360612931</v>
       </c>
     </row>
     <row r="8">
@@ -2733,10 +2733,10 @@
         <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
-        <v>97.2175664130404</v>
+        <v>81.02854677001049</v>
       </c>
       <c r="D8" t="n">
-        <v>31.04286240828414</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>31.72812230584841</v>
+        <v>30.50780990946962</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -2758,7 +2758,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
         <v>25.62361508084176</v>
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>19.90198946049134</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2876,7 +2876,7 @@
         <v>29.96293993361265</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.491495746929157</v>
+        <v>4.025165587411922</v>
       </c>
       <c r="C2" t="n">
-        <v>2.923644663247001</v>
+        <v>1.869247628885927</v>
       </c>
       <c r="D2" t="n">
-        <v>13.43030859409637</v>
+        <v>12.73621296719387</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.73665493555038</v>
+        <v>19.08026663203676</v>
       </c>
       <c r="C3" t="n">
-        <v>16.72898088036565</v>
+        <v>15.19254572321939</v>
       </c>
       <c r="D3" t="n">
-        <v>67.92221491831558</v>
+        <v>75.42276737876121</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.48856017047897</v>
+        <v>52.22505087511333</v>
       </c>
       <c r="C4" t="n">
-        <v>65.60038159777187</v>
+        <v>72.24975879863551</v>
       </c>
       <c r="D4" t="n">
-        <v>155.8455758152514</v>
+        <v>172.3350102557808</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>70.66129101316419</v>
+        <v>66.04707680320418</v>
       </c>
       <c r="C5" t="n">
-        <v>144.9550485320416</v>
+        <v>171.2167996206437</v>
       </c>
       <c r="D5" t="n">
-        <v>142.4515918862122</v>
+        <v>153.1280981698963</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.32464936159877</v>
+        <v>54.017722183068</v>
       </c>
       <c r="C6" t="n">
-        <v>211.4419483067483</v>
+        <v>229.8369550412208</v>
       </c>
       <c r="D6" t="n">
-        <v>71.16492758544281</v>
+        <v>74.46556336712058</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.45180923259856</v>
+        <v>23.1162314441954</v>
       </c>
       <c r="C7" t="n">
-        <v>215.2324761928452</v>
+        <v>199.0630915039002</v>
       </c>
       <c r="D7" t="n">
-        <v>39.82459562277186</v>
+        <v>40.8426679920758</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.009678608322226</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>152.7108553955914</v>
+        <v>125.0059351817464</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>33.29597338953057</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>63.78905708343648</v>
+        <v>56.35624521458389</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -3069,10 +3069,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
         <v>24.76949457814703</v>
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.98900515327081</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
         <v>11.82515109765283</v>
@@ -3173,7 +3173,7 @@
         <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.205406254365836</v>
+        <v>2.869648539513427</v>
       </c>
       <c r="C2" t="n">
-        <v>2.122538536581604</v>
+        <v>2.249183990429443</v>
       </c>
       <c r="D2" t="n">
-        <v>10.32798584867644</v>
+        <v>10.1257458216016</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.48001787411446</v>
+        <v>17.00877897607599</v>
       </c>
       <c r="C3" t="n">
-        <v>14.52986602285279</v>
+        <v>11.67788894201581</v>
       </c>
       <c r="D3" t="n">
-        <v>64.13266877992288</v>
+        <v>69.91025401941538</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.94953962311847</v>
+        <v>47.36245449597887</v>
       </c>
       <c r="C4" t="n">
-        <v>56.99830821316132</v>
+        <v>59.30836056125406</v>
       </c>
       <c r="D4" t="n">
-        <v>155.3861178896639</v>
+        <v>171.9393659309694</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>76.30634031258334</v>
+        <v>72.77204857729483</v>
       </c>
       <c r="C5" t="n">
-        <v>139.2363681548039</v>
+        <v>162.454701360241</v>
       </c>
       <c r="D5" t="n">
-        <v>158.9694970101648</v>
+        <v>171.9285667062227</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>69.43410638285567</v>
+        <v>63.55736462523426</v>
       </c>
       <c r="C6" t="n">
-        <v>228.6294053649972</v>
+        <v>255.1552465860418</v>
       </c>
       <c r="D6" t="n">
-        <v>85.73602701187396</v>
+        <v>90.28446412564944</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.83487076370406</v>
+        <v>21.55917958525995</v>
       </c>
       <c r="C7" t="n">
-        <v>255.1768450355352</v>
+        <v>247.6311321806942</v>
       </c>
       <c r="D7" t="n">
-        <v>44.91495746929157</v>
+        <v>46.83132898798135</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>192.5158160642783</v>
+        <v>161.4729536559941</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>76.87968097186344</v>
+        <v>65.89686940445439</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
         <v>16.1301147807751</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3470,7 +3470,7 @@
         <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.104507225006667</v>
+        <v>4.520948178056562</v>
       </c>
       <c r="C2" t="n">
-        <v>5.011822030179967</v>
+        <v>10.06978620245953</v>
       </c>
       <c r="D2" t="n">
-        <v>17.01172421918873</v>
+        <v>13.31740760810798</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.25006792714245</v>
+        <v>13.51866588747858</v>
       </c>
       <c r="C3" t="n">
-        <v>11.57480543306989</v>
+        <v>10.21017612416683</v>
       </c>
       <c r="D3" t="n">
-        <v>58.93922342445726</v>
+        <v>63.12146864454867</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.28739970209961</v>
+        <v>40.18980576875168</v>
       </c>
       <c r="C4" t="n">
-        <v>47.50284441768617</v>
+        <v>45.56291095409447</v>
       </c>
       <c r="D4" t="n">
-        <v>150.804301353944</v>
+        <v>168.123312604562</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>74.63736921536378</v>
+        <v>72.08482518432207</v>
       </c>
       <c r="C5" t="n">
-        <v>124.0929098167969</v>
+        <v>139.0891059991669</v>
       </c>
       <c r="D5" t="n">
-        <v>174.2602175038089</v>
+        <v>186.3602579586508</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>82.51589454194442</v>
+        <v>76.96116603131597</v>
       </c>
       <c r="C6" t="n">
-        <v>226.536319259543</v>
+        <v>257.3690876591183</v>
       </c>
       <c r="D6" t="n">
-        <v>108.1159476778843</v>
+        <v>114.8379742088622</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43.95677170994669</v>
+        <v>40.06414206260808</v>
       </c>
       <c r="C7" t="n">
-        <v>287.5156144134251</v>
+        <v>300.391235554622</v>
       </c>
       <c r="D7" t="n">
-        <v>54.97590794241288</v>
+        <v>57.49114556069321</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.01659189998096</v>
+        <v>11.18210635137117</v>
       </c>
       <c r="C8" t="n">
-        <v>253.4332611127928</v>
+        <v>226.1455836732528</v>
       </c>
       <c r="D8" t="n">
-        <v>37.30150402285756</v>
+        <v>37.55184968744049</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.773437264497239</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>137.2296758473234</v>
+        <v>116.0406151465645</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>52.24370408149402</v>
+        <v>47.83074815090461</v>
       </c>
       <c r="D10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.72062817711293</v>
+        <v>28.07602084605028</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
         <v>16.3902779224005</v>
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
         <v>11.36962016288231</v>
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.727156253677396</v>
+        <v>7.436738859669589</v>
       </c>
       <c r="C2" t="n">
-        <v>7.407286428542184</v>
+        <v>5.089380098815464</v>
       </c>
       <c r="D2" t="n">
-        <v>8.455792976677778</v>
+        <v>7.093127163183205</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.319689898685966</v>
+        <v>3.237803928605981</v>
       </c>
       <c r="C2" t="n">
-        <v>2.806816686441631</v>
+        <v>5.719662124941918</v>
       </c>
       <c r="D2" t="n">
-        <v>12.52022847225957</v>
+        <v>9.800787331495908</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.07674055184727</v>
+        <v>18.37831702350029</v>
       </c>
       <c r="C3" t="n">
-        <v>15.79141182280995</v>
+        <v>20.40071729424872</v>
       </c>
       <c r="D3" t="n">
-        <v>65.91944960165209</v>
+        <v>69.20339567235766</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>56.57713844803943</v>
+        <v>55.16047651081129</v>
       </c>
       <c r="C4" t="n">
-        <v>68.26779011021046</v>
+        <v>68.75277347610837</v>
       </c>
       <c r="D4" t="n">
-        <v>155.513745091216</v>
+        <v>172.4243492968673</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.23464736797755</v>
+        <v>45.35674393620265</v>
       </c>
       <c r="C5" t="n">
-        <v>189.133695223148</v>
+        <v>212.2783973507666</v>
       </c>
       <c r="D5" t="n">
-        <v>159.435827169682</v>
+        <v>170.2595956090031</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.29062268265284</v>
+        <v>24.87552333020568</v>
       </c>
       <c r="C6" t="n">
-        <v>235.9954583899611</v>
+        <v>250.808067751637</v>
       </c>
       <c r="D6" t="n">
-        <v>84.44797402390215</v>
+        <v>89.19766941704822</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.964919124554372</v>
+        <v>7.366053024963818</v>
       </c>
       <c r="C7" t="n">
-        <v>178.222551238149</v>
+        <v>158.9989494412922</v>
       </c>
       <c r="D7" t="n">
-        <v>33.23706852727577</v>
+        <v>33.71616140694821</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.919316761802514</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>101.1396484915064</v>
+        <v>85.53476873250335</v>
       </c>
       <c r="D8" t="n">
-        <v>24.78422079371073</v>
+        <v>24.86766934857171</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>39.82655911818034</v>
+        <v>36.49843440078366</v>
       </c>
       <c r="D9" t="n">
-        <v>20.41249826669968</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>21.92242623583128</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
         <v>13.23494080095125</v>
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
         <v>9.365873098514571</v>
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.222137023067036</v>
+        <v>8.229009256996765</v>
       </c>
       <c r="C2" t="n">
-        <v>6.042657119639118</v>
+        <v>5.266094685579891</v>
       </c>
       <c r="D2" t="n">
-        <v>18.4980902434184</v>
+        <v>22.29450861574082</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.64615422031042</v>
+        <v>15.79141182280995</v>
       </c>
       <c r="C3" t="n">
-        <v>18.66302385773187</v>
+        <v>12.82162501746335</v>
       </c>
       <c r="D3" t="n">
-        <v>10.23962855529423</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39760897911447</v>
+        <v>13.39863425598977</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14042347889342</v>
+        <v>70.14579110488764</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576189291660526</v>
+        <v>1.576309912469385</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.543929285881738</v>
+        <v>5.746169312956581</v>
       </c>
       <c r="C2" t="n">
-        <v>9.075275778057515</v>
+        <v>6.780931393232719</v>
       </c>
       <c r="D2" t="n">
-        <v>17.87468045122167</v>
+        <v>23.0848155176595</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.38799563182252</v>
+        <v>23.37541283811656</v>
       </c>
       <c r="C3" t="n">
-        <v>21.73098543350315</v>
+        <v>17.64691498383642</v>
       </c>
       <c r="D3" t="n">
-        <v>23.30178176029805</v>
+        <v>25.62361508084175</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.75142220884308</v>
+        <v>18.27621526225862</v>
       </c>
       <c r="C4" t="n">
-        <v>28.99690019263379</v>
+        <v>20.08852152429823</v>
       </c>
       <c r="D4" t="n">
-        <v>20.43311496848886</v>
+        <v>19.83326712119406</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>3.043417883165113</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.375068680751288</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.3346624606237</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43814021436994</v>
+        <v>15.44094327402311</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12857172227444</v>
+        <v>86.14420984454999</v>
       </c>
       <c r="D21" t="n">
-        <v>3.25013478197262</v>
+        <v>3.250724899794339</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.067601722872788</v>
+        <v>6.080945280104743</v>
       </c>
       <c r="C2" t="n">
-        <v>8.06113039957056</v>
+        <v>4.80761850769663</v>
       </c>
       <c r="D2" t="n">
-        <v>29.03027961457818</v>
+        <v>29.65957989300039</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.89297380470387</v>
+        <v>21.41682616814417</v>
       </c>
       <c r="C3" t="n">
-        <v>29.81567777797563</v>
+        <v>22.94835258676919</v>
       </c>
       <c r="D3" t="n">
-        <v>32.19150722225291</v>
+        <v>38.14580704850982</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.27539774547039</v>
+        <v>33.61700488881928</v>
       </c>
       <c r="C4" t="n">
-        <v>43.41877396801944</v>
+        <v>34.26790361673491</v>
       </c>
       <c r="D4" t="n">
-        <v>27.5164246546296</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.8067599331794</v>
+        <v>15.58524480491812</v>
       </c>
       <c r="C5" t="n">
-        <v>32.86400439966199</v>
+        <v>23.4392264388926</v>
       </c>
       <c r="D5" t="n">
-        <v>30.01693605734623</v>
+        <v>29.82058651649687</v>
       </c>
     </row>
     <row r="6">
@@ -5196,7 +5196,7 @@
         <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.34724525432967</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.66867766424586</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5246,7 +5246,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
         <v>29.89421759431538</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72750878837972</v>
+        <v>16.73343266344857</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0378036091163</v>
+        <v>102.0739392470363</v>
       </c>
       <c r="D21" t="n">
-        <v>4.18187719709493</v>
+        <v>5.020029799034573</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.716536955379929</v>
+        <v>6.23900666048848</v>
       </c>
       <c r="C2" t="n">
-        <v>6.302820261264523</v>
+        <v>4.727115195948392</v>
       </c>
       <c r="D2" t="n">
-        <v>35.28499423833461</v>
+        <v>32.69121680371454</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.07597978832128</v>
+        <v>21.28429022807085</v>
       </c>
       <c r="C3" t="n">
-        <v>30.61089341841555</v>
+        <v>20.45962215650353</v>
       </c>
       <c r="D3" t="n">
-        <v>47.0944373727195</v>
+        <v>52.19952543480291</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.24085664937251</v>
+        <v>37.57344813693393</v>
       </c>
       <c r="C4" t="n">
-        <v>60.099649210877</v>
+        <v>47.19653913396116</v>
       </c>
       <c r="D4" t="n">
-        <v>36.92254940901829</v>
+        <v>40.29190752999335</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.63177216211199</v>
+        <v>32.83946070705581</v>
       </c>
       <c r="C5" t="n">
-        <v>58.41398840268523</v>
+        <v>44.93950116189775</v>
       </c>
       <c r="D5" t="n">
-        <v>32.7658296292373</v>
+        <v>32.83946070705581</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.06041069377357</v>
+        <v>13.56480802957818</v>
       </c>
       <c r="C6" t="n">
-        <v>32.88560284915541</v>
+        <v>25.03652995370216</v>
       </c>
       <c r="D6" t="n">
-        <v>38.19882142453915</v>
+        <v>37.99756314516856</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.08008670558751</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>39.64493579289469</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.62700229231099</v>
+        <v>31.37665662772806</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>40.05530633326986</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>42.26718391093791</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.82238578098934</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
         <v>48.68486865359933</v>
@@ -5574,7 +5574,7 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5585,7 +5585,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
         <v>34.28066633689012</v>
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5619,7 +5619,7 @@
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04444758726981</v>
+        <v>18.05693219264691</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7185390217125</v>
+        <v>117.7999862091727</v>
       </c>
       <c r="D21" t="n">
-        <v>6.014815862423268</v>
+        <v>6.878831311484538</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.247662463377454</v>
+        <v>7.391578465274236</v>
       </c>
       <c r="C2" t="n">
-        <v>3.7394770054761</v>
+        <v>9.750718198579321</v>
       </c>
       <c r="D2" t="n">
-        <v>37.50767104074939</v>
+        <v>29.24331886639974</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.07950586851076</v>
+        <v>18.98209186161208</v>
       </c>
       <c r="C3" t="n">
-        <v>25.46653544816226</v>
+        <v>18.08870145074748</v>
       </c>
       <c r="D3" t="n">
-        <v>59.67553420264237</v>
+        <v>61.56048979479624</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.70710469343173</v>
+        <v>28.65230674844316</v>
       </c>
       <c r="C4" t="n">
-        <v>57.80235958293945</v>
+        <v>41.36397602303086</v>
       </c>
       <c r="D4" t="n">
-        <v>44.860961345558</v>
+        <v>49.28962523941536</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.40963513904496</v>
+        <v>27.58711048933538</v>
       </c>
       <c r="C5" t="n">
-        <v>63.49453277216247</v>
+        <v>49.89732706834415</v>
       </c>
       <c r="D5" t="n">
-        <v>31.07231483941155</v>
+        <v>31.78408192499049</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.31450342272425</v>
+        <v>15.73839744678062</v>
       </c>
       <c r="C6" t="n">
-        <v>43.06927178530758</v>
+        <v>33.36862271964485</v>
       </c>
       <c r="D6" t="n">
-        <v>30.67176177607885</v>
+        <v>30.95352336719769</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.827073535332318</v>
+        <v>6.228207435741766</v>
       </c>
       <c r="C7" t="n">
-        <v>21.85861263505523</v>
+        <v>18.56484908730718</v>
       </c>
       <c r="D7" t="n">
-        <v>31.26081039862693</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>30.06405994715006</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06830573313655</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
         <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
         <v>30.43908757017236</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>29.49955501720816</v>
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.0475238666185</v>
+        <v>7.056262347992134</v>
       </c>
       <c r="C21" t="n">
-        <v>66.07053624954844</v>
+        <v>66.15245951242625</v>
       </c>
       <c r="D21" t="n">
-        <v>4.404702416636563</v>
+        <v>5.2921967609941</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.216246536841556</v>
+        <v>6.777986150119979</v>
       </c>
       <c r="C2" t="n">
-        <v>2.322815068247953</v>
+        <v>6.781913140936966</v>
       </c>
       <c r="D2" t="n">
-        <v>26.9627189494344</v>
+        <v>32.85909566114074</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.18321127226244</v>
+        <v>23.26742059064941</v>
       </c>
       <c r="C3" t="n">
-        <v>18.55994034878595</v>
+        <v>30.99377502307181</v>
       </c>
       <c r="D3" t="n">
-        <v>76.7628529950581</v>
+        <v>71.25033963571227</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.50512670826415</v>
+        <v>34.2423781764245</v>
       </c>
       <c r="C4" t="n">
-        <v>61.6056501891916</v>
+        <v>43.92928277422778</v>
       </c>
       <c r="D4" t="n">
-        <v>65.72800879932396</v>
+        <v>69.64616388697297</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.76078202199582</v>
+        <v>36.93825737228624</v>
       </c>
       <c r="C5" t="n">
-        <v>89.60902170512763</v>
+        <v>66.21888265144737</v>
       </c>
       <c r="D5" t="n">
-        <v>40.42346172236243</v>
+        <v>43.51596699073988</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.07427833482005</v>
+        <v>28.01515248838698</v>
       </c>
       <c r="C6" t="n">
-        <v>76.51839781670066</v>
+        <v>60.0554705641859</v>
       </c>
       <c r="D6" t="n">
-        <v>34.09315252537899</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.27108553955913</v>
+        <v>13.47448724078747</v>
       </c>
       <c r="C7" t="n">
-        <v>44.79518424937346</v>
+        <v>36.17151241526948</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>32.99752208743954</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.425538724295373</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>24.95111790343269</v>
+        <v>22.44766125760332</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -6171,7 +6171,7 @@
         <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.909319358310797</v>
+        <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.263933477925113</v>
+        <v>7.277904007829691</v>
       </c>
       <c r="C21" t="n">
-        <v>75.36330983347307</v>
+        <v>75.50825408123305</v>
       </c>
       <c r="D21" t="n">
-        <v>5.447950108443835</v>
+        <v>6.36816600685098</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.662139921018856</v>
+        <v>6.273367830137119</v>
       </c>
       <c r="C2" t="n">
-        <v>5.528221322613789</v>
+        <v>3.580433877388117</v>
       </c>
       <c r="D2" t="n">
-        <v>23.14764737073129</v>
+        <v>29.79211583307371</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.37112599440108</v>
+        <v>23.39013905368026</v>
       </c>
       <c r="C3" t="n">
-        <v>12.95416095753666</v>
+        <v>28.20070280448963</v>
       </c>
       <c r="D3" t="n">
-        <v>80.179335005837</v>
+        <v>81.00400307740432</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.55014823393926</v>
+        <v>40.71307729511523</v>
       </c>
       <c r="C4" t="n">
-        <v>52.41649167744146</v>
+        <v>63.77531261557705</v>
       </c>
       <c r="D4" t="n">
-        <v>87.51397210426492</v>
+        <v>89.72192269111601</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.21010367537139</v>
+        <v>44.79223900626073</v>
       </c>
       <c r="C5" t="n">
-        <v>103.2553147941583</v>
+        <v>74.80917506360696</v>
       </c>
       <c r="D5" t="n">
-        <v>54.85515297479054</v>
+        <v>58.26672624704821</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.47178834404877</v>
+        <v>40.21140421824511</v>
       </c>
       <c r="C6" t="n">
-        <v>112.1411132652962</v>
+        <v>84.97124555026569</v>
       </c>
       <c r="D6" t="n">
-        <v>38.84284791852506</v>
+        <v>40.77492740048278</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.52976821186155</v>
+        <v>24.01453059358123</v>
       </c>
       <c r="C7" t="n">
-        <v>79.46953141566655</v>
+        <v>63.4199199466397</v>
       </c>
       <c r="D7" t="n">
-        <v>36.23139902522853</v>
+        <v>35.87207936547421</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.76624623539802</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>43.64359419229195</v>
+        <v>36.63391558396972</v>
       </c>
       <c r="D8" t="n">
-        <v>33.12907627980861</v>
+        <v>33.71321616383547</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>27.95624762613216</v>
+        <v>26.40312275801371</v>
       </c>
       <c r="D9" t="n">
         <v>32.72655972106742</v>
@@ -6490,10 +6490,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
         <v>34.02246669067321</v>
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.467167410064114</v>
+        <v>7.486367391710383</v>
       </c>
       <c r="C21" t="n">
-        <v>84.00563336322129</v>
+        <v>84.22163315674182</v>
       </c>
       <c r="D21" t="n">
-        <v>6.5337714838061</v>
+        <v>7.486367391710383</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_57_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_57_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497627946917</v>
+        <v>10.84497644648654</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907175811766</v>
+        <v>37.78907234008584</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.782314051564466</v>
+        <v>1.178097245096172</v>
       </c>
       <c r="C2" t="n">
-        <v>5.899321954819084</v>
+        <v>2.34834050855837</v>
       </c>
       <c r="D2" t="n">
-        <v>30.71004993654448</v>
+        <v>20.83464977952581</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.25131171675396</v>
+        <v>9.92056055141402</v>
       </c>
       <c r="C3" t="n">
-        <v>20.18473279931442</v>
+        <v>32.51057522613313</v>
       </c>
       <c r="D3" t="n">
-        <v>85.21570072862315</v>
+        <v>82.98713343998288</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.72958707963818</v>
+        <v>14.99619618237003</v>
       </c>
       <c r="C4" t="n">
-        <v>66.77455185205106</v>
+        <v>110.8186991076757</v>
       </c>
       <c r="D4" t="n">
-        <v>107.0154085014236</v>
+        <v>90.9216183857056</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.33344403320799</v>
+        <v>13.13087554430109</v>
       </c>
       <c r="C5" t="n">
-        <v>97.58572180213298</v>
+        <v>119.5523266846554</v>
       </c>
       <c r="D5" t="n">
-        <v>76.23270923476484</v>
+        <v>51.19814277647117</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.39507315439728</v>
+        <v>9.579894098040377</v>
       </c>
       <c r="C6" t="n">
-        <v>102.5209675113817</v>
+        <v>82.19388129495147</v>
       </c>
       <c r="D6" t="n">
-        <v>48.74475526355839</v>
+        <v>30.30949687321178</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.17151241526948</v>
+        <v>5.809001166028376</v>
       </c>
       <c r="C7" t="n">
-        <v>93.00390526641308</v>
+        <v>46.47200932822701</v>
       </c>
       <c r="D7" t="n">
-        <v>39.58504918293564</v>
+        <v>28.86534600026472</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.19178495969339</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>60.91744504851459</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>35.549084370777</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.431249284071605</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>36.38749691020377</v>
+        <v>31.17343485294896</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>38.43542262126263</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>37.5351599764683</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.85539932116455</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.680683395993269</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93.12828617641837</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.640768820492427</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.647233779005905</v>
+        <v>0.9503317777109125</v>
       </c>
       <c r="C2" t="n">
-        <v>9.460120878122265</v>
+        <v>5.224861282001525</v>
       </c>
       <c r="D2" t="n">
-        <v>30.9790488075081</v>
+        <v>20.57939537642164</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.94482650657971</v>
+        <v>6.778967897824225</v>
       </c>
       <c r="C3" t="n">
-        <v>21.48554850744145</v>
+        <v>19.08517537055799</v>
       </c>
       <c r="D3" t="n">
-        <v>88.77944489503906</v>
+        <v>80.36095833112267</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.04040019125691</v>
+        <v>17.38282485139402</v>
       </c>
       <c r="C4" t="n">
-        <v>58.51707191163113</v>
+        <v>94.3675528276119</v>
       </c>
       <c r="D4" t="n">
-        <v>122.4455371690707</v>
+        <v>110.9208008689174</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.04583301359268</v>
+        <v>17.96598298771663</v>
       </c>
       <c r="C5" t="n">
-        <v>108.8021893231528</v>
+        <v>166.7007601811084</v>
       </c>
       <c r="D5" t="n">
-        <v>93.06968236259763</v>
+        <v>71.00490270965058</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.82025202579416</v>
+        <v>13.4038014060817</v>
       </c>
       <c r="C6" t="n">
-        <v>127.4367424974615</v>
+        <v>137.8619213688584</v>
       </c>
       <c r="D6" t="n">
-        <v>59.77370897306707</v>
+        <v>38.64158963915446</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>47.01098881785852</v>
+        <v>8.384125394267761</v>
       </c>
       <c r="C7" t="n">
-        <v>118.2760546691345</v>
+        <v>82.52374852357838</v>
       </c>
       <c r="D7" t="n">
-        <v>43.59745205019235</v>
+        <v>31.38058361854505</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.62147165898401</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="C8" t="n">
-        <v>90.45823346930109</v>
+        <v>45.47946239923349</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>31.87734795689393</v>
       </c>
     </row>
     <row r="9">
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.86874890726719</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>54.35937038414588</v>
+        <v>35.27812200440487</v>
       </c>
       <c r="D9" t="n">
         <v>35.27812200440487</v>
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.8329640215578</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>36.44247478164161</v>
+        <v>34.30717352490479</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>39.14718970684157</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>31.98534020436108</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>38.38240824523329</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>28.63954402828795</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>46.33947338815369</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.859907356215337</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>101.1963072112725</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.824884195269172</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.172468800777949</v>
+        <v>0.5134540493210819</v>
       </c>
       <c r="C2" t="n">
-        <v>9.84005723966578</v>
+        <v>2.1853703896534</v>
       </c>
       <c r="D2" t="n">
-        <v>29.78720709455247</v>
+        <v>14.00953973960198</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.79051219056371</v>
+        <v>5.988660995905544</v>
       </c>
       <c r="C3" t="n">
-        <v>28.37250865273282</v>
+        <v>21.02412708644545</v>
       </c>
       <c r="D3" t="n">
-        <v>91.02764713776426</v>
+        <v>81.00400307740432</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.71682435948296</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="C4" t="n">
-        <v>55.58164627593317</v>
+        <v>85.17839431586177</v>
       </c>
       <c r="D4" t="n">
-        <v>133.1534593792906</v>
+        <v>123.2113003783832</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.32839642596651</v>
+        <v>17.86780821729195</v>
       </c>
       <c r="C5" t="n">
-        <v>107.0595871481147</v>
+        <v>191.8825887950391</v>
       </c>
       <c r="D5" t="n">
-        <v>110.7411410390402</v>
+        <v>80.47876805563229</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>67.86429180376503</v>
+        <v>11.14970867713103</v>
       </c>
       <c r="C6" t="n">
-        <v>147.3210604992764</v>
+        <v>175.215458020041</v>
       </c>
       <c r="D6" t="n">
-        <v>70.88316599432396</v>
+        <v>39.20511282139213</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>57.49114556069321</v>
+        <v>4.251949307092936</v>
       </c>
       <c r="C7" t="n">
-        <v>145.7041220303819</v>
+        <v>78.99043853599412</v>
       </c>
       <c r="D7" t="n">
-        <v>48.92736033654828</v>
+        <v>33.0574086973986</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>37.30150402285756</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>118.663845012312</v>
+        <v>41.55738032076748</v>
       </c>
       <c r="D8" t="n">
-        <v>40.72289477215769</v>
+        <v>36.04977569994287</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18.97031088916111</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>79.43124325520091</v>
+        <v>26.18124777685393</v>
       </c>
       <c r="D9" t="n">
-        <v>36.49843440078366</v>
+        <v>40.60312155223957</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.110618695410402</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>48.11545498513618</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>36.60544490054656</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>30.38607319414302</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>40.12893741108837</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.023669328270234</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109.3224945976819</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.03254532637157</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.492117641734909</v>
+        <v>0.3514656781203581</v>
       </c>
       <c r="C2" t="n">
-        <v>6.690610604442013</v>
+        <v>3.794454876913922</v>
       </c>
       <c r="D2" t="n">
-        <v>24.52798464290231</v>
+        <v>12.85598618711198</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.25746424488669</v>
+        <v>3.82881604656256</v>
       </c>
       <c r="C3" t="n">
-        <v>41.96480561802991</v>
+        <v>14.08807955594173</v>
       </c>
       <c r="D3" t="n">
-        <v>99.62284828844508</v>
+        <v>73.85197105196632</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.98413747247858</v>
+        <v>15.51946770873358</v>
       </c>
       <c r="C4" t="n">
-        <v>83.85107141972007</v>
+        <v>68.39541731176254</v>
       </c>
       <c r="D4" t="n">
-        <v>126.7210484210655</v>
+        <v>134.5573585963636</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.2145293878071</v>
+        <v>22.80109043113217</v>
       </c>
       <c r="C5" t="n">
-        <v>88.01368168572657</v>
+        <v>175.9782759862408</v>
       </c>
       <c r="D5" t="n">
-        <v>72.10936887692823</v>
+        <v>103.5498391054324</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.70321876034376</v>
+        <v>16.66418553188536</v>
       </c>
       <c r="C6" t="n">
-        <v>95.95994760390025</v>
+        <v>241.1476703418483</v>
       </c>
       <c r="D6" t="n">
-        <v>32.20132469929539</v>
+        <v>53.29319237733387</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.73316991308989</v>
+        <v>7.545712854840985</v>
       </c>
       <c r="C7" t="n">
-        <v>83.42204767296421</v>
+        <v>158.819289611415</v>
       </c>
       <c r="D7" t="n">
-        <v>28.62579956042849</v>
+        <v>36.47094546506476</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.18487166803466</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>58.4974369575462</v>
+        <v>69.1788519797515</v>
       </c>
       <c r="D8" t="n">
-        <v>26.8704346652352</v>
+        <v>37.1346069131356</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.545311944213482</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>36.72030938194344</v>
+        <v>37.16405934426299</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>28.61303684027329</v>
+        <v>29.60951076008381</v>
       </c>
       <c r="D10" t="n">
-        <v>28.47068342315751</v>
+        <v>32.02951885105219</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.09685853201771</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>30.8092064546734</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>37.61173629739955</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>47.22206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.250386722311942</v>
+        <v>0.2817615911188346</v>
       </c>
       <c r="C2" t="n">
-        <v>2.969786805346601</v>
+        <v>3.476368620737956</v>
       </c>
       <c r="D2" t="n">
-        <v>16.91158595335556</v>
+        <v>10.17286971140545</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.60107594137308</v>
+        <v>2.699806186678729</v>
       </c>
       <c r="C3" t="n">
-        <v>34.45934441906304</v>
+        <v>14.75566799482956</v>
       </c>
       <c r="D3" t="n">
-        <v>97.01139939514857</v>
+        <v>69.00213739298707</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.30016242225481</v>
+        <v>12.53299119241478</v>
       </c>
       <c r="C4" t="n">
-        <v>97.2008767020682</v>
+        <v>54.59891682398212</v>
       </c>
       <c r="D4" t="n">
-        <v>145.6226369709294</v>
+        <v>140.0198028227928</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.21515128261285</v>
+        <v>24.3473430653209</v>
       </c>
       <c r="C5" t="n">
-        <v>120.6322491593268</v>
+        <v>161.1293419595078</v>
       </c>
       <c r="D5" t="n">
-        <v>92.70152697350508</v>
+        <v>121.7367153266045</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.74725853831463</v>
+        <v>20.85035774279376</v>
       </c>
       <c r="C6" t="n">
-        <v>117.5750868083023</v>
+        <v>267.5125049393964</v>
       </c>
       <c r="D6" t="n">
-        <v>41.0164373357275</v>
+        <v>64.84541761320608</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.29589127407256</v>
+        <v>8.204465564390594</v>
       </c>
       <c r="C7" t="n">
-        <v>107.0173719968321</v>
+        <v>226.4312722551886</v>
       </c>
       <c r="D7" t="n">
-        <v>31.32069700858599</v>
+        <v>40.36357511240336</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>76.2719791429347</v>
+        <v>105.9796646734432</v>
       </c>
       <c r="D8" t="n">
-        <v>28.12216298814988</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>42.59999638267758</v>
+        <v>47.48124596819272</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>32.88363935374691</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>27.54293184264426</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.51842920776709</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.26269177857742</v>
+        <v>22.99842171968578</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.405903770210438</v>
+        <v>1.403899217072939</v>
       </c>
       <c r="C2" t="n">
-        <v>4.787001805907448</v>
+        <v>3.778746913645973</v>
       </c>
       <c r="D2" t="n">
-        <v>14.35118794067987</v>
+        <v>10.7422833798686</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.15099352447153</v>
+        <v>1.840776945462769</v>
       </c>
       <c r="C3" t="n">
-        <v>22.38384765682728</v>
+        <v>14.17643684932394</v>
       </c>
       <c r="D3" t="n">
-        <v>89.47157702653307</v>
+        <v>61.89428401424016</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.92776124717579</v>
+        <v>9.010480429577225</v>
       </c>
       <c r="C4" t="n">
-        <v>91.44488991206916</v>
+        <v>45.81816535719864</v>
       </c>
       <c r="D4" t="n">
-        <v>158.5895606486212</v>
+        <v>142.1894652491783</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.3454049321082</v>
+        <v>22.40839134943345</v>
       </c>
       <c r="C5" t="n">
-        <v>149.2992821233337</v>
+        <v>132.4377653028947</v>
       </c>
       <c r="D5" t="n">
-        <v>118.6442100582271</v>
+        <v>140.6844460185679</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.46928506929254</v>
+        <v>26.00256969468102</v>
       </c>
       <c r="C6" t="n">
-        <v>153.7613254391355</v>
+        <v>266.1842002955505</v>
       </c>
       <c r="D6" t="n">
-        <v>56.43282153551517</v>
+        <v>83.36117931530093</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.6743471662931</v>
+        <v>14.55244622005047</v>
       </c>
       <c r="C7" t="n">
-        <v>137.260110026155</v>
+        <v>296.9178121769968</v>
       </c>
       <c r="D7" t="n">
-        <v>35.03366682604743</v>
+        <v>47.60985491744906</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.1890196430299</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>106.2300103380261</v>
+        <v>189.0944253149781</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79113408536946</v>
+        <v>41.55738032076748</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>64.78749449865549</v>
+        <v>81.7609305573786</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>42.59999638267758</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>40.00131020953629</v>
+        <v>41.85190463204153</v>
       </c>
       <c r="D10" t="n">
-        <v>30.60598467989432</v>
+        <v>34.44952694202058</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>31.62994753542373</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>33.22921454564179</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>32.96708790860789</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.806235849364884</v>
+        <v>0.9542587685278997</v>
       </c>
       <c r="C2" t="n">
-        <v>2.270782439922872</v>
+        <v>1.995893082733765</v>
       </c>
       <c r="D2" t="n">
-        <v>9.918597056005526</v>
+        <v>7.820602212030092</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.12292375167588</v>
+        <v>3.382120841130261</v>
       </c>
       <c r="C3" t="n">
-        <v>22.00587479069226</v>
+        <v>16.56699250916493</v>
       </c>
       <c r="D3" t="n">
-        <v>86.19744843286996</v>
+        <v>65.90963212460962</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>54.95627298832795</v>
+        <v>15.14934882423253</v>
       </c>
       <c r="C4" t="n">
-        <v>88.02448091047326</v>
+        <v>68.15292562881358</v>
       </c>
       <c r="D4" t="n">
-        <v>168.365804287511</v>
+        <v>145.8268404934127</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.55433726666352</v>
+        <v>16.07611865704152</v>
       </c>
       <c r="C5" t="n">
-        <v>176.444606145758</v>
+        <v>212.4256595064036</v>
       </c>
       <c r="D5" t="n">
-        <v>125.2464633692869</v>
+        <v>128.3880560228766</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.62021217383928</v>
+        <v>9.016370915802709</v>
       </c>
       <c r="C6" t="n">
-        <v>186.1639084178015</v>
+        <v>258.1741207766007</v>
       </c>
       <c r="D6" t="n">
-        <v>54.98376192404687</v>
+        <v>68.30706001838034</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.71970318267092</v>
+        <v>3.952516257297658</v>
       </c>
       <c r="C7" t="n">
-        <v>142.2306986527566</v>
+        <v>132.9482741091031</v>
       </c>
       <c r="D7" t="n">
-        <v>34.91389360612931</v>
+        <v>36.17151241526948</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>2.253110981246429</v>
       </c>
       <c r="C8" t="n">
-        <v>81.02854677001049</v>
+        <v>60.24985660962675</v>
       </c>
       <c r="D8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>30.50780990946962</v>
+        <v>31.94999728700819</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>26.29218526743382</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>21.14586380177204</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>13.78864650614645</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>34.40043955680824</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.025165587411922</v>
+        <v>0.460439673291754</v>
       </c>
       <c r="C2" t="n">
-        <v>1.869247628885927</v>
+        <v>1.227184630308513</v>
       </c>
       <c r="D2" t="n">
-        <v>12.73621296719387</v>
+        <v>6.346017160251383</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.08026663203676</v>
+        <v>3.342850932960389</v>
       </c>
       <c r="C3" t="n">
-        <v>15.19254572321939</v>
+        <v>11.8202423591316</v>
       </c>
       <c r="D3" t="n">
-        <v>75.42276737876121</v>
+        <v>57.32424845097125</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>52.22505087511333</v>
+        <v>10.23570156447724</v>
       </c>
       <c r="C4" t="n">
-        <v>72.24975879863551</v>
+        <v>52.08466095340604</v>
       </c>
       <c r="D4" t="n">
-        <v>172.3350102557808</v>
+        <v>139.8283620204647</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>66.04707680320418</v>
+        <v>15.24163310843173</v>
       </c>
       <c r="C5" t="n">
-        <v>171.2167996206437</v>
+        <v>154.7479818819035</v>
       </c>
       <c r="D5" t="n">
-        <v>153.1280981698963</v>
+        <v>135.4075521082413</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.017722183068</v>
+        <v>9.016370915802709</v>
       </c>
       <c r="C6" t="n">
-        <v>229.8369550412208</v>
+        <v>245.8973657349944</v>
       </c>
       <c r="D6" t="n">
-        <v>74.46556336712058</v>
+        <v>74.02279515250527</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.1162314441954</v>
+        <v>3.233876937788993</v>
       </c>
       <c r="C7" t="n">
-        <v>199.0630915039002</v>
+        <v>171.2158178729395</v>
       </c>
       <c r="D7" t="n">
-        <v>40.8426679920758</v>
+        <v>35.39298648580176</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.842781498600267</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>125.0059351817464</v>
+        <v>69.34574908947344</v>
       </c>
       <c r="D8" t="n">
-        <v>33.29597338953057</v>
+        <v>27.03733177495716</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>56.35624521458389</v>
+        <v>30.06405994715006</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>20.85624822901923</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>18.07888397370501</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.98900515327081</v>
+        <v>13.68261775408779</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.869648539513427</v>
+        <v>0.5635231822376692</v>
       </c>
       <c r="C2" t="n">
-        <v>2.249183990429443</v>
+        <v>6.401976779393451</v>
       </c>
       <c r="D2" t="n">
-        <v>10.1257458216016</v>
+        <v>11.25573742918968</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.00877897607599</v>
+        <v>2.390555659840983</v>
       </c>
       <c r="C3" t="n">
-        <v>11.67788894201581</v>
+        <v>7.608544707912781</v>
       </c>
       <c r="D3" t="n">
-        <v>69.91025401941538</v>
+        <v>49.65189014228244</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.36245449597887</v>
+        <v>8.27024266057513</v>
       </c>
       <c r="C4" t="n">
-        <v>59.30836056125406</v>
+        <v>39.10497455555895</v>
       </c>
       <c r="D4" t="n">
-        <v>171.9393659309694</v>
+        <v>135.9102069328157</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>72.77204857729483</v>
+        <v>15.70796326794897</v>
       </c>
       <c r="C5" t="n">
-        <v>162.454701360241</v>
+        <v>123.6511233498858</v>
       </c>
       <c r="D5" t="n">
-        <v>171.9285667062227</v>
+        <v>155.6315548157257</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>63.55736462523426</v>
+        <v>14.77235770580176</v>
       </c>
       <c r="C6" t="n">
-        <v>255.1552465860418</v>
+        <v>247.1854187229662</v>
       </c>
       <c r="D6" t="n">
-        <v>90.28446412564944</v>
+        <v>98.576305235718</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.55917958525995</v>
+        <v>6.707300315414209</v>
       </c>
       <c r="C7" t="n">
-        <v>247.6311321806942</v>
+        <v>270.08861091534</v>
       </c>
       <c r="D7" t="n">
-        <v>46.83132898798135</v>
+        <v>47.4301950875719</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>161.4729536559941</v>
+        <v>149.5398103108741</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>30.45872252425729</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>65.89686940445439</v>
+        <v>57.68749510154256</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>22.63124807829746</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>20.4988920646734</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>17.05884810899257</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>13.66887328622834</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.520948178056562</v>
+        <v>0.3583379120500858</v>
       </c>
       <c r="C2" t="n">
-        <v>10.06978620245953</v>
+        <v>8.588328916751097</v>
       </c>
       <c r="D2" t="n">
-        <v>13.31740760810798</v>
+        <v>12.65669140314988</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.51866588747858</v>
+        <v>2.130392518215579</v>
       </c>
       <c r="C3" t="n">
-        <v>10.21017612416683</v>
+        <v>17.00387023755476</v>
       </c>
       <c r="D3" t="n">
-        <v>63.12146864454867</v>
+        <v>47.18770340462294</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.18980576875168</v>
+        <v>6.406885517914685</v>
       </c>
       <c r="C4" t="n">
-        <v>45.56291095409447</v>
+        <v>28.44810322595982</v>
       </c>
       <c r="D4" t="n">
-        <v>168.123312604562</v>
+        <v>130.5881526280937</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>72.08482518432207</v>
+        <v>14.23534171157875</v>
       </c>
       <c r="C5" t="n">
-        <v>139.0891059991669</v>
+        <v>96.1621876309751</v>
       </c>
       <c r="D5" t="n">
-        <v>186.3602579586508</v>
+        <v>166.6516727958961</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>76.96116603131597</v>
+        <v>18.07299348747954</v>
       </c>
       <c r="C6" t="n">
-        <v>257.3690876591183</v>
+        <v>223.2759351337394</v>
       </c>
       <c r="D6" t="n">
-        <v>114.8379742088622</v>
+        <v>122.7675504160637</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.06414206260808</v>
+        <v>11.79766216193392</v>
       </c>
       <c r="C7" t="n">
-        <v>300.391235554622</v>
+        <v>315.9018675340174</v>
       </c>
       <c r="D7" t="n">
-        <v>57.49114556069321</v>
+        <v>62.46173418729481</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.18210635137117</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>226.1455836732528</v>
+        <v>251.6808414607123</v>
       </c>
       <c r="D8" t="n">
-        <v>37.55184968744049</v>
+        <v>35.04839304161113</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.884374755077128</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>116.0406151465645</v>
+        <v>118.481239939322</v>
       </c>
       <c r="D9" t="n">
-        <v>33.83593462686631</v>
+        <v>24.96093538047515</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>47.83074815090461</v>
+        <v>46.12250714551515</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>21.35301256736813</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.07602084605028</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>19.01350778814797</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>14.75370449942107</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.436738859669589</v>
+        <v>3.461642405174254</v>
       </c>
       <c r="C2" t="n">
-        <v>5.089380098815464</v>
+        <v>12.09022297779947</v>
       </c>
       <c r="D2" t="n">
-        <v>7.093127163183205</v>
+        <v>10.56262354999143</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.237803928605981</v>
+        <v>0.4663301595172349</v>
       </c>
       <c r="C2" t="n">
-        <v>5.719662124941918</v>
+        <v>9.820422285580845</v>
       </c>
       <c r="D2" t="n">
-        <v>9.800787331495908</v>
+        <v>11.04564342048086</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.37831702350029</v>
+        <v>1.65915362017711</v>
       </c>
       <c r="C3" t="n">
-        <v>20.40071729424872</v>
+        <v>25.15728492132452</v>
       </c>
       <c r="D3" t="n">
-        <v>69.20339567235766</v>
+        <v>46.65755964432967</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>55.16047651081129</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C4" t="n">
-        <v>68.75277347610837</v>
+        <v>35.26339578884118</v>
       </c>
       <c r="D4" t="n">
-        <v>172.4243492968673</v>
+        <v>124.1429789497134</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.35674393620265</v>
+        <v>12.37002107350981</v>
       </c>
       <c r="C5" t="n">
-        <v>212.2783973507666</v>
+        <v>75.44731107136739</v>
       </c>
       <c r="D5" t="n">
-        <v>170.2595956090031</v>
+        <v>174.5547418150829</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.87552333020568</v>
+        <v>18.6365166697172</v>
       </c>
       <c r="C6" t="n">
-        <v>250.808067751637</v>
+        <v>190.6318422198287</v>
       </c>
       <c r="D6" t="n">
-        <v>89.19766941704822</v>
+        <v>141.6053253651515</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.366053024963818</v>
+        <v>16.10949807898591</v>
       </c>
       <c r="C7" t="n">
-        <v>158.9989494412922</v>
+        <v>322.7888276793087</v>
       </c>
       <c r="D7" t="n">
-        <v>33.71616140694821</v>
+        <v>79.46953141566655</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>85.53476873250335</v>
+        <v>329.1211003717007</v>
       </c>
       <c r="D8" t="n">
-        <v>24.86766934857171</v>
+        <v>41.47393176590651</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>36.49843440078366</v>
+        <v>201.906232855399</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>27.62343515439249</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>21.92242623583128</v>
+        <v>86.5508776063988</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>22.49183990429443</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.17036643664921</v>
+        <v>35.7169632282032</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52575910558656</v>
+        <v>19.36890045708532</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>15.4046032273367</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.229009256996765</v>
+        <v>3.711006322052943</v>
       </c>
       <c r="C2" t="n">
-        <v>5.266094685579891</v>
+        <v>8.25453469730718</v>
       </c>
       <c r="D2" t="n">
-        <v>22.29450861574082</v>
+        <v>23.96053446984766</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.79141182280995</v>
+        <v>5.723589115758905</v>
       </c>
       <c r="C3" t="n">
-        <v>12.82162501746335</v>
+        <v>23.8711954287612</v>
       </c>
       <c r="D3" t="n">
-        <v>9.095892479846698</v>
+        <v>10.234719816773</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39863425598977</v>
+        <v>11.67774486590941</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14579110488764</v>
+        <v>59.945756978335</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576309912469385</v>
+        <v>0.778516324393961</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.746169312956581</v>
+        <v>2.162790192455723</v>
       </c>
       <c r="C2" t="n">
-        <v>6.780931393232719</v>
+        <v>4.001603642509999</v>
       </c>
       <c r="D2" t="n">
-        <v>23.0848155176595</v>
+        <v>24.34047083139117</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.37541283811656</v>
+        <v>10.25435477085794</v>
       </c>
       <c r="C3" t="n">
-        <v>17.64691498383642</v>
+        <v>29.48188355853172</v>
       </c>
       <c r="D3" t="n">
-        <v>25.62361508084175</v>
+        <v>28.74557278034661</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18.27621526225862</v>
+        <v>7.210936887692823</v>
       </c>
       <c r="C4" t="n">
-        <v>20.08852152429823</v>
+        <v>39.34746623850791</v>
       </c>
       <c r="D4" t="n">
-        <v>19.83326712119406</v>
+        <v>19.60353815840031</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.043417883165113</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.105088062083415</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.3346624606237</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44094327402311</v>
+        <v>13.62703874004702</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14420984454999</v>
+        <v>73.746327299078</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250724899794339</v>
+        <v>1.603181028240826</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.080945280104743</v>
+        <v>1.414698441819654</v>
       </c>
       <c r="C2" t="n">
-        <v>4.80761850769663</v>
+        <v>5.524294331796802</v>
       </c>
       <c r="D2" t="n">
-        <v>29.65957989300039</v>
+        <v>27.27785996249763</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.41682616814417</v>
+        <v>8.688467182584272</v>
       </c>
       <c r="C3" t="n">
-        <v>22.94835258676919</v>
+        <v>20.67560665143783</v>
       </c>
       <c r="D3" t="n">
-        <v>38.14580704850982</v>
+        <v>42.24460371374025</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.61700488881928</v>
+        <v>14.88133170097315</v>
       </c>
       <c r="C4" t="n">
-        <v>34.26790361673491</v>
+        <v>60.72502249848221</v>
       </c>
       <c r="D4" t="n">
-        <v>28.20561154301086</v>
+        <v>30.12001956629214</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>15.58524480491812</v>
+        <v>7.068583470577036</v>
       </c>
       <c r="C5" t="n">
-        <v>23.4392264388926</v>
+        <v>45.62672455487052</v>
       </c>
       <c r="D5" t="n">
-        <v>29.82058651649687</v>
+        <v>26.97351817418112</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>10.54593383901924</v>
       </c>
       <c r="D6" t="n">
-        <v>36.34724525432967</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.886960145291375</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.66867766424586</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.95717262057418</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73343266344857</v>
+        <v>14.83481900818425</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0739392470363</v>
+        <v>87.36060082597395</v>
       </c>
       <c r="D21" t="n">
-        <v>5.020029799034573</v>
+        <v>2.472469834697376</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.23900666048848</v>
+        <v>1.770091110756999</v>
       </c>
       <c r="C2" t="n">
-        <v>4.727115195948392</v>
+        <v>10.96317661332413</v>
       </c>
       <c r="D2" t="n">
-        <v>32.69121680371454</v>
+        <v>27.35345453572463</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.28429022807085</v>
+        <v>6.543348448804991</v>
       </c>
       <c r="C3" t="n">
-        <v>20.45962215650353</v>
+        <v>21.17138924208247</v>
       </c>
       <c r="D3" t="n">
-        <v>52.19952543480291</v>
+        <v>54.26610435224244</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.57344813693393</v>
+        <v>16.1448409963388</v>
       </c>
       <c r="C4" t="n">
-        <v>47.19653913396116</v>
+        <v>55.50506995500192</v>
       </c>
       <c r="D4" t="n">
-        <v>40.29190752999335</v>
+        <v>44.50360518121217</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.83946070705581</v>
+        <v>14.97165248976386</v>
       </c>
       <c r="C5" t="n">
-        <v>44.93950116189775</v>
+        <v>83.59581701661591</v>
       </c>
       <c r="D5" t="n">
-        <v>32.83946070705581</v>
+        <v>31.53864499892879</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.56480802957818</v>
+        <v>7.245298057341462</v>
       </c>
       <c r="C6" t="n">
-        <v>25.03652995370216</v>
+        <v>44.35732477327939</v>
       </c>
       <c r="D6" t="n">
-        <v>37.99756314516856</v>
+        <v>33.73088762251191</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>39.64493579289469</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.37665662772806</v>
+        <v>25.70215489718149</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>27.40156017323271</v>
       </c>
       <c r="D9" t="n">
-        <v>42.26718391093791</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.4902616239802</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05693219264691</v>
+        <v>16.07344322145249</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7999862091727</v>
+        <v>100.6705128080445</v>
       </c>
       <c r="D21" t="n">
-        <v>6.878831311484538</v>
+        <v>3.383882783463682</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.391578465274236</v>
+        <v>3.535273482992764</v>
       </c>
       <c r="C2" t="n">
-        <v>9.750718198579321</v>
+        <v>9.195048997975626</v>
       </c>
       <c r="D2" t="n">
-        <v>29.24331886639974</v>
+        <v>30.12394655710913</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.98209186161208</v>
+        <v>6.263550353094651</v>
       </c>
       <c r="C3" t="n">
-        <v>18.08870145074748</v>
+        <v>33.49723166890117</v>
       </c>
       <c r="D3" t="n">
-        <v>61.56048979479624</v>
+        <v>62.98402396595412</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.65230674844316</v>
+        <v>14.23043297305752</v>
       </c>
       <c r="C4" t="n">
-        <v>41.36397602303086</v>
+        <v>54.10117073792898</v>
       </c>
       <c r="D4" t="n">
-        <v>49.28962523941536</v>
+        <v>60.76331065894783</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.58711048933538</v>
+        <v>19.78221624057323</v>
       </c>
       <c r="C5" t="n">
-        <v>49.89732706834415</v>
+        <v>93.85508052599508</v>
       </c>
       <c r="D5" t="n">
-        <v>31.78408192499049</v>
+        <v>39.61351986635881</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.73839744678062</v>
+        <v>13.6050596854523</v>
       </c>
       <c r="C6" t="n">
-        <v>33.36862271964485</v>
+        <v>90.16370915802707</v>
       </c>
       <c r="D6" t="n">
-        <v>30.95352336719769</v>
+        <v>36.34724525432967</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.228207435741766</v>
+        <v>7.665486074759095</v>
       </c>
       <c r="C7" t="n">
-        <v>18.56484908730718</v>
+        <v>41.14210104187108</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>37.18958478457343</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>30.39687241888974</v>
       </c>
       <c r="D9" t="n">
-        <v>30.06405994715006</v>
+        <v>38.49530923122167</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>6.930157044278233</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>46.37874329632356</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.056262347992134</v>
+        <v>17.33652213579439</v>
       </c>
       <c r="C21" t="n">
-        <v>66.15245951242625</v>
+        <v>114.421046096243</v>
       </c>
       <c r="D21" t="n">
-        <v>5.2921967609941</v>
+        <v>4.334130533948597</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.777986150119979</v>
+        <v>2.68998870963626</v>
       </c>
       <c r="C2" t="n">
-        <v>6.781913140936966</v>
+        <v>7.455392066050278</v>
       </c>
       <c r="D2" t="n">
-        <v>32.85909566114074</v>
+        <v>36.33644602958294</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.26742059064941</v>
+        <v>9.262789589568655</v>
       </c>
       <c r="C3" t="n">
-        <v>30.99377502307181</v>
+        <v>34.55751918948773</v>
       </c>
       <c r="D3" t="n">
-        <v>71.25033963571227</v>
+        <v>71.2699745897972</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.2423781764245</v>
+        <v>12.99244911800229</v>
       </c>
       <c r="C4" t="n">
-        <v>43.92928277422778</v>
+        <v>69.44196036448963</v>
       </c>
       <c r="D4" t="n">
-        <v>69.64616388697297</v>
+        <v>76.70394813280329</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.93825737228624</v>
+        <v>20.73942025221387</v>
       </c>
       <c r="C5" t="n">
-        <v>66.21888265144737</v>
+        <v>95.86766331970105</v>
       </c>
       <c r="D5" t="n">
-        <v>43.51596699073988</v>
+        <v>50.63363784652926</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.01515248838698</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="C6" t="n">
-        <v>60.0554705641859</v>
+        <v>119.2254046991412</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>40.49316580936395</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.47448724078747</v>
+        <v>11.67788894201581</v>
       </c>
       <c r="C7" t="n">
-        <v>36.17151241526948</v>
+        <v>83.96102716259571</v>
       </c>
       <c r="D7" t="n">
-        <v>32.99752208743954</v>
+        <v>39.40538935305847</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.175193059712437</v>
+        <v>8.261406931236909</v>
       </c>
       <c r="C8" t="n">
-        <v>22.44766125760332</v>
+        <v>39.05392367493811</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>31.61718481526852</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>39.49374664644068</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>34.02246669067321</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>43.84485247166256</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>47.08952863419825</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>45.12897846881738</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20021977840412</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.277904007829691</v>
+        <v>17.73009526020206</v>
       </c>
       <c r="C21" t="n">
-        <v>75.50825408123305</v>
+        <v>127.6566858734548</v>
       </c>
       <c r="D21" t="n">
-        <v>6.36816600685098</v>
+        <v>5.319028578060617</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.273367830137119</v>
+        <v>2.467131980772234</v>
       </c>
       <c r="C2" t="n">
-        <v>3.580433877388117</v>
+        <v>4.651520622721387</v>
       </c>
       <c r="D2" t="n">
-        <v>29.79211583307371</v>
+        <v>28.76128074361456</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.39013905368026</v>
+        <v>10.56851403621691</v>
       </c>
       <c r="C3" t="n">
-        <v>28.20070280448963</v>
+        <v>48.96466674930967</v>
       </c>
       <c r="D3" t="n">
-        <v>81.00400307740432</v>
+        <v>78.16675221213104</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.71307729511523</v>
+        <v>9.954921721062657</v>
       </c>
       <c r="C4" t="n">
-        <v>63.77531261557705</v>
+        <v>90.51321134073893</v>
       </c>
       <c r="D4" t="n">
-        <v>89.72192269111601</v>
+        <v>69.96523189085319</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.79223900626073</v>
+        <v>11.04466167277662</v>
       </c>
       <c r="C5" t="n">
-        <v>74.80917506360696</v>
+        <v>71.22579594310611</v>
       </c>
       <c r="D5" t="n">
-        <v>58.26672624704821</v>
+        <v>38.77903431774902</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.21140421824511</v>
+        <v>7.245298057341462</v>
       </c>
       <c r="C6" t="n">
-        <v>84.97124555026569</v>
+        <v>55.2655235151657</v>
       </c>
       <c r="D6" t="n">
-        <v>40.77492740048278</v>
+        <v>25.92206638293279</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.01453059358123</v>
+        <v>5.449681506274044</v>
       </c>
       <c r="C7" t="n">
-        <v>63.4199199466397</v>
+        <v>27.42806736124739</v>
       </c>
       <c r="D7" t="n">
-        <v>35.87207936547421</v>
+        <v>26.70942804173872</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>36.63391558396972</v>
+        <v>23.28214680621311</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71321616383547</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>26.40312275801371</v>
+        <v>25.95937279569415</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>36.86953503298896</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>96.83959354690535</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.486367391710383</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.22163315674182</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.486367391710383</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
